--- a/template.xlsx
+++ b/template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Windows\ServiceProfiles\NetworkService\AppData\Local\Packages\oice_16_974fa576_32c1d314_3ba8\AC\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/57eee4f248eb746f/ドキュメント/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACC465AD-AEB9-9E4C-97C5-0C5A2D9D6442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{CCF6B523-1BE9-764D-B386-A8EB190AE591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8366F2E4-5604-4F9B-B3CE-86FDD9341454}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{6FB1A243-9338-410E-A20A-1FE9187612EE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{6FB1A243-9338-410E-A20A-1FE9187612EE}"/>
   </bookViews>
   <sheets>
     <sheet name="電車・バス・他" sheetId="6" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">車!$A$1:$H$62</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">電車・バス・他!$A$1:$L$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">電車・バス・他!$A$1:$AV$59</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="21">
   <si>
     <t>円</t>
     <rPh sb="0" eb="1">
@@ -254,7 +254,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -390,76 +390,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="dashed">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -481,19 +411,6 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="dashed">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -602,28 +519,6 @@
       </left>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -703,13 +598,265 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF505050"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="dashed">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF505050"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF505050"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF505050"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF505050"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF505050"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF505050"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF505050"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="dashed">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF505050"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF505050"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF505050"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF505050"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -734,19 +881,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -755,122 +902,134 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -878,38 +1037,32 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -958,8 +1111,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5130597" y="10684126"/>
-          <a:ext cx="2221896" cy="504625"/>
+          <a:off x="5126566" y="9749367"/>
+          <a:ext cx="2226734" cy="509058"/>
           <a:chOff x="379" y="1016"/>
           <a:chExt cx="216" cy="70"/>
         </a:xfrm>
@@ -1322,8 +1475,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="12478255" y="10684126"/>
-          <a:ext cx="2217459" cy="504625"/>
+          <a:off x="12479867" y="9749367"/>
+          <a:ext cx="2226733" cy="509058"/>
           <a:chOff x="379" y="1016"/>
           <a:chExt cx="216" cy="70"/>
         </a:xfrm>
@@ -1626,6 +1779,2190 @@
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5AB87EE-8EFC-2CF5-6B7C-80B606F78AF6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>2886</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>2886</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>289</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="4097" name="Group 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87B76F25-2EF5-4EBD-AF8D-D90A02C5BA5C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr>
+          <a:grpSpLocks/>
+        </xdr:cNvGrpSpPr>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="19836053" y="9749367"/>
+          <a:ext cx="2226733" cy="520989"/>
+          <a:chOff x="379" y="1016"/>
+          <a:chExt cx="216" cy="70"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4098" name="Group 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01FFA10B-1147-EF3B-3D4D-1DAF9D9B0153}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="379" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4105" name="Rectangle 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{122CE6E3-1699-6FBE-F776-E1DBD2B11766}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="72" cy="24"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>業務部</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4106" name="Rectangle 47">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0A6D3B9-3D61-3A53-EEE1-58F251BF5318}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4099" name="Group 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BB6F8DB-F876-9B42-9BD4-4CECFC3F745E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="451" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4103" name="Rectangle 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F18A864E-36F3-A50F-835D-A4C6BFB8B453}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="74" cy="24"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>総務受付</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4104" name="Rectangle 50">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D1A0915-FC30-7D04-8212-C63E8D2F5058}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4100" name="Group 51">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AE85988-E243-834C-A5DA-B126AEC847EB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="523" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4101" name="Rectangle 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D7952E8-83F1-F2BB-17C2-07FDCED32B43}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="72" cy="22"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>最終確認</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4102" name="Rectangle 53">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1428B4F-A879-992B-79EA-63F978FDDD1F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>289</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="4107" name="Group 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{217890F3-D133-4378-AA1F-80FE51304F82}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr>
+          <a:grpSpLocks/>
+        </xdr:cNvGrpSpPr>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="27186467" y="9749367"/>
+          <a:ext cx="2226733" cy="520989"/>
+          <a:chOff x="379" y="1016"/>
+          <a:chExt cx="216" cy="70"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4108" name="Group 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF1248AA-7AA6-AAEC-B8AE-602A7CC9D3E8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="379" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4115" name="Rectangle 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2F3F82A-3384-99A4-13A5-10F78F3A6D22}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="72" cy="24"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>業務部</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4116" name="Rectangle 47">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B48F2DE-56E6-3F44-AD11-2E3688012967}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4109" name="Group 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{306DC4B3-7626-9C67-46FF-3D6530FC80FB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="451" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4113" name="Rectangle 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B443F4BD-07C5-B3F2-5540-B9349DF0F5F6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="74" cy="24"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>総務受付</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4114" name="Rectangle 50">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{061D6E6D-7448-6CBF-5BF7-98BB5358ABCB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4110" name="Group 51">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E234AF85-81A9-195F-BD89-B51D5F26B0CE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="523" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4111" name="Rectangle 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DC0C372-A490-6EA5-B5FF-CD38D0C5637E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="72" cy="22"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>最終確認</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4112" name="Rectangle 53">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{717B49CF-36B9-FC4C-0B48-987988454540}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>2886</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>2887</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>289</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="4117" name="Group 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D74C1FA-7D92-415F-B648-B771577DA502}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr>
+          <a:grpSpLocks/>
+        </xdr:cNvGrpSpPr>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="34542653" y="9749367"/>
+          <a:ext cx="2226734" cy="520989"/>
+          <a:chOff x="379" y="1016"/>
+          <a:chExt cx="216" cy="70"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4118" name="Group 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD154BE2-1D44-7AA2-F5F7-F22DC8EAF32D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="379" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4125" name="Rectangle 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5651EA71-EF50-396B-FB13-5B73E4DD2CF0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="72" cy="24"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>業務部</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4126" name="Rectangle 47">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D1AF6E7-17E3-14A0-27FF-4CE9162FD1C8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4119" name="Group 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66689D20-E7A3-9FE5-B0EE-9332A621E710}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="451" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4123" name="Rectangle 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29C7FD29-B496-FDB9-5AB5-AAA41E3FC87F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="74" cy="24"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>総務受付</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4124" name="Rectangle 50">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26D8F9EB-B4CB-C715-016C-7AC5A51545A9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4120" name="Group 51">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{085F97DB-D7EC-58B6-9F3E-6069CBBA2D37}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="523" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4121" name="Rectangle 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A6473A2-0444-A550-4D10-860B0A175175}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="72" cy="22"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>最終確認</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4122" name="Rectangle 53">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A072CD1-E723-B520-5F08-324FAF9DE777}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>289</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="4127" name="Group 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B67C8A0B-008B-4F55-8064-1600A6F800F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr>
+          <a:grpSpLocks/>
+        </xdr:cNvGrpSpPr>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="41893067" y="9749367"/>
+          <a:ext cx="2226733" cy="520989"/>
+          <a:chOff x="379" y="1016"/>
+          <a:chExt cx="216" cy="70"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4128" name="Group 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A572E759-4A01-10A8-BD8F-A5064A1E2296}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="379" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4135" name="Rectangle 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C016EE08-30A9-AE73-1F5A-B38E034DCE98}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="72" cy="24"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>業務部</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4136" name="Rectangle 47">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F81787FD-8A2E-7D91-7255-76D2AEC04F52}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4129" name="Group 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31B79033-31E2-05F8-41A8-88F20BAA2943}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="451" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4133" name="Rectangle 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCC257F9-6F25-953C-3B02-F54452B67443}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="74" cy="24"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>総務受付</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4134" name="Rectangle 50">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B368334B-9E6B-FA50-F747-7F219F03F67B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4130" name="Group 51">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99BFD44B-B59B-648C-1925-28C512B138C4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="523" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4131" name="Rectangle 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCAA7B70-73DA-7A3A-A9B1-A2B998701C24}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="72" cy="22"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>最終確認</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4132" name="Rectangle 53">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FF146BF-A4E6-9B8C-F81B-AB97CF4886A0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>2886</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>2886</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>289</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="4137" name="Group 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71A396A7-1E37-4AE1-A98B-95661CD51114}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr>
+          <a:grpSpLocks/>
+        </xdr:cNvGrpSpPr>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="49249253" y="9749367"/>
+          <a:ext cx="2226733" cy="520989"/>
+          <a:chOff x="379" y="1016"/>
+          <a:chExt cx="216" cy="70"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4138" name="Group 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D45909D7-1132-98C6-D85C-1EB2C5E6F770}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="379" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4147" name="Rectangle 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{362B2712-6FD7-BBC8-1BA5-DFB0BB0D129F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="72" cy="24"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>業務部</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4149" name="Rectangle 47">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6650B5A4-3F10-AF83-ABB1-9C250D07DB67}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4139" name="Group 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F037615-ADAE-1C10-1E0A-8F42E18D5269}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="451" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4144" name="Rectangle 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF03FAF4-A05A-47F7-B7A1-311D3F8C7A1E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="74" cy="24"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>総務受付</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4146" name="Rectangle 50">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4ED632DA-0AA4-C883-B7C7-2C934EFDF34D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4140" name="Group 51">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F3FE1CF-5E0E-637E-588C-B88065FD965E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="523" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4141" name="Rectangle 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58D11652-D438-8D9C-D50D-305CCEB805C6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="72" cy="22"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>最終確認</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4143" name="Rectangle 53">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB14DE5D-427D-5968-1A4D-FCDAF9C23F14}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>289</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="4150" name="Group 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8045FD29-2DCD-411E-8226-B9D5725D0810}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr>
+          <a:grpSpLocks/>
+        </xdr:cNvGrpSpPr>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="56599667" y="9749367"/>
+          <a:ext cx="2226733" cy="520989"/>
+          <a:chOff x="379" y="1016"/>
+          <a:chExt cx="216" cy="70"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4151" name="Group 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8DD389D-9F96-BA31-B394-3EE8F8464DED}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="379" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4158" name="Rectangle 46">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F3FF03A-D6C6-95E5-A0DD-8BC82ABA1D44}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="72" cy="24"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>業務部</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4159" name="Rectangle 47">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B433DC55-1277-2746-22FA-D83A8D10E8CC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4152" name="Group 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D87A34B2-E2D1-1EDD-D2B1-ECF692428FC7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="451" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4156" name="Rectangle 49">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{502CE02D-55FA-5BB1-CB23-0E2065A4CE27}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="74" cy="24"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>総務受付</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4157" name="Rectangle 50">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BC8987B-F325-3B3B-2732-C8C72A6996AF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1039"/>
+              <a:ext cx="72" cy="47"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="4153" name="Group 51">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{366AA096-244F-9A8D-1680-0AA6E0E03FA8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr>
+            <a:grpSpLocks/>
+          </xdr:cNvGrpSpPr>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="523" y="1016"/>
+            <a:ext cx="72" cy="70"/>
+            <a:chOff x="72" y="1016"/>
+            <a:chExt cx="72" cy="70"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4154" name="Rectangle 52">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0359CD44-8B50-8857-F87C-A093E26263EE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr>
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="72" y="1016"/>
+              <a:ext cx="72" cy="22"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="27432" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="ＭＳ Ｐゴシック"/>
+                  <a:ea typeface="ＭＳ Ｐゴシック"/>
+                </a:rPr>
+                <a:t>最終確認</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4155" name="Rectangle 53">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4029231-C3F4-48DF-926D-3FD62BC6005A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3077,7 +5414,7 @@
   <sheetPr>
     <tabColor indexed="41"/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:AV57"/>
   <sheetFormatPr defaultColWidth="8.99609375" defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <cols>
     <col min="1" max="1" width="7.6328125" style="1" customWidth="1"/>
@@ -3090,40 +5427,148 @@
     <col min="9" max="9" width="22.76953125" style="1" customWidth="1"/>
     <col min="10" max="10" width="20.04296875" style="1" customWidth="1"/>
     <col min="11" max="12" width="15.953125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.99609375" style="1"/>
+    <col min="13" max="13" width="7.6328125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="22.90625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="22.76953125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20.04296875" style="1" customWidth="1"/>
+    <col min="17" max="18" width="15.953125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.6328125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="22.90625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="22.76953125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="20.04296875" style="1" customWidth="1"/>
+    <col min="23" max="24" width="15.953125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="7.6328125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="22.90625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="22.76953125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="20.04296875" style="1" customWidth="1"/>
+    <col min="29" max="30" width="15.953125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="7.6328125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="22.90625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="22.76953125" style="1" customWidth="1"/>
+    <col min="34" max="34" width="20.04296875" style="1" customWidth="1"/>
+    <col min="35" max="36" width="15.953125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="7.6328125" style="1" customWidth="1"/>
+    <col min="38" max="38" width="22.90625" style="1" customWidth="1"/>
+    <col min="39" max="39" width="22.76953125" style="1" customWidth="1"/>
+    <col min="40" max="40" width="20.04296875" style="1" customWidth="1"/>
+    <col min="41" max="42" width="15.953125" style="1" customWidth="1"/>
+    <col min="43" max="43" width="7.6328125" style="1" customWidth="1"/>
+    <col min="44" max="44" width="22.90625" style="1" customWidth="1"/>
+    <col min="45" max="45" width="22.76953125" style="1" customWidth="1"/>
+    <col min="46" max="46" width="20.04296875" style="1" customWidth="1"/>
+    <col min="47" max="48" width="15.953125" style="1" customWidth="1"/>
+    <col min="49" max="16384" width="8.99609375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.1">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.1">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.1">
-      <c r="A2" s="50" t="s">
+    <row r="2" spans="1:48" ht="18.75" x14ac:dyDescent="0.1">
+      <c r="A2" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="30" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="50" t="s">
+      <c r="F2" s="57"/>
+      <c r="G2" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="30" t="s">
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="30"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="57"/>
+      <c r="S2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="X2" s="57"/>
+      <c r="Y2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z2" s="56"/>
+      <c r="AA2" s="56"/>
+      <c r="AB2" s="56"/>
+      <c r="AC2" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD2" s="57"/>
+      <c r="AE2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF2" s="56"/>
+      <c r="AG2" s="56"/>
+      <c r="AH2" s="56"/>
+      <c r="AI2" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ2" s="57"/>
+      <c r="AK2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="AP2" s="57"/>
+      <c r="AQ2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="AR2" s="56"/>
+      <c r="AS2" s="56"/>
+      <c r="AT2" s="56"/>
+      <c r="AU2" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="AV2" s="57"/>
     </row>
-    <row r="3" spans="1:12" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:48" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3136,15 +5581,51 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="2"/>
+      <c r="AE3" s="2"/>
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="2"/>
+      <c r="AH3" s="2"/>
+      <c r="AI3" s="2"/>
+      <c r="AJ3" s="2"/>
+      <c r="AK3" s="2"/>
+      <c r="AL3" s="2"/>
+      <c r="AM3" s="2"/>
+      <c r="AN3" s="2"/>
+      <c r="AO3" s="2"/>
+      <c r="AP3" s="2"/>
+      <c r="AQ3" s="2"/>
+      <c r="AR3" s="2"/>
+      <c r="AS3" s="2"/>
+      <c r="AT3" s="2"/>
+      <c r="AU3" s="2"/>
+      <c r="AV3" s="2"/>
     </row>
-    <row r="4" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:48" ht="14.25" thickBot="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="18" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="5" t="s">
@@ -3153,17 +5634,89 @@
       <c r="G4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="54"/>
-      <c r="I4" s="55"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="59"/>
       <c r="J4" s="4"/>
-      <c r="K4" s="20" t="s">
+      <c r="K4" s="18" t="s">
         <v>16</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>0</v>
       </c>
+      <c r="M4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" s="58"/>
+      <c r="O4" s="59"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="58"/>
+      <c r="U4" s="59"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="58"/>
+      <c r="AA4" s="59"/>
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="58"/>
+      <c r="AG4" s="59"/>
+      <c r="AH4" s="4"/>
+      <c r="AI4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="58"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="4"/>
+      <c r="AO4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR4" s="58"/>
+      <c r="AS4" s="59"/>
+      <c r="AT4" s="4"/>
+      <c r="AU4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AV4" s="5" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:48" ht="14.25" thickBot="1" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
@@ -3172,942 +5725,3462 @@
         <v>2</v>
       </c>
       <c r="H5" s="7"/>
+      <c r="M5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N5" s="7"/>
+      <c r="S5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="Y5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z5" s="7"/>
+      <c r="AE5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF5" s="7"/>
+      <c r="AK5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL5" s="7"/>
+      <c r="AQ5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR5" s="7"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.1">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A6" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="53"/>
-      <c r="E6" s="19" t="s">
+      <c r="D6" s="47"/>
+      <c r="E6" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="53" t="s">
+      <c r="I6" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="53"/>
-      <c r="K6" s="19" t="s">
+      <c r="J6" s="47"/>
+      <c r="K6" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="22" t="s">
         <v>18</v>
       </c>
+      <c r="M6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="O6" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="R6" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="S6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="T6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="U6" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="V6" s="49"/>
+      <c r="W6" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="X6" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA6" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB6" s="47"/>
+      <c r="AC6" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD6" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG6" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH6" s="47"/>
+      <c r="AI6" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ6" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM6" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN6" s="49"/>
+      <c r="AO6" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP6" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS6" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="AT6" s="49"/>
+      <c r="AU6" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV6" s="22" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A7" s="34"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="L7" s="25" t="s">
+    <row r="7" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A7" s="29"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="29"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M7" s="29"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R7" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S7" s="29"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="52"/>
+      <c r="V7" s="53"/>
+      <c r="W7" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X7" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="50"/>
+      <c r="AA7" s="52"/>
+      <c r="AB7" s="53"/>
+      <c r="AC7" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD7" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="50"/>
+      <c r="AG7" s="52"/>
+      <c r="AH7" s="53"/>
+      <c r="AI7" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ7" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK7" s="29"/>
+      <c r="AL7" s="50"/>
+      <c r="AM7" s="52"/>
+      <c r="AN7" s="53"/>
+      <c r="AO7" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP7" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ7" s="29"/>
+      <c r="AR7" s="50"/>
+      <c r="AS7" s="52"/>
+      <c r="AT7" s="53"/>
+      <c r="AU7" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV7" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A8" s="35"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="26"/>
+    <row r="8" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A8" s="39"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="55"/>
+      <c r="Q8" s="37"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="39"/>
+      <c r="T8" s="51"/>
+      <c r="U8" s="54"/>
+      <c r="V8" s="55"/>
+      <c r="W8" s="37"/>
+      <c r="X8" s="38"/>
+      <c r="Y8" s="39"/>
+      <c r="Z8" s="51"/>
+      <c r="AA8" s="54"/>
+      <c r="AB8" s="55"/>
+      <c r="AC8" s="37"/>
+      <c r="AD8" s="43"/>
+      <c r="AE8" s="39"/>
+      <c r="AF8" s="51"/>
+      <c r="AG8" s="54"/>
+      <c r="AH8" s="55"/>
+      <c r="AI8" s="37"/>
+      <c r="AJ8" s="43"/>
+      <c r="AK8" s="39"/>
+      <c r="AL8" s="51"/>
+      <c r="AM8" s="54"/>
+      <c r="AN8" s="55"/>
+      <c r="AO8" s="37"/>
+      <c r="AP8" s="38"/>
+      <c r="AQ8" s="39"/>
+      <c r="AR8" s="51"/>
+      <c r="AS8" s="54"/>
+      <c r="AT8" s="55"/>
+      <c r="AU8" s="37"/>
+      <c r="AV8" s="38"/>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A9" s="34"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="25" t="s">
+    <row r="9" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A9" s="29"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="29"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="29"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="29"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="33"/>
+      <c r="V9" s="34"/>
+      <c r="W9" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="33"/>
+      <c r="AB9" s="34"/>
+      <c r="AC9" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="29"/>
+      <c r="AF9" s="31"/>
+      <c r="AG9" s="33"/>
+      <c r="AH9" s="34"/>
+      <c r="AI9" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ9" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="29"/>
+      <c r="AL9" s="31"/>
+      <c r="AM9" s="33"/>
+      <c r="AN9" s="34"/>
+      <c r="AO9" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP9" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ9" s="29"/>
+      <c r="AR9" s="31"/>
+      <c r="AS9" s="33"/>
+      <c r="AT9" s="34"/>
+      <c r="AU9" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV9" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A10" s="35"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="26"/>
+    <row r="10" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A10" s="39"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="42"/>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="39"/>
+      <c r="T10" s="40"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="42"/>
+      <c r="W10" s="37"/>
+      <c r="X10" s="38"/>
+      <c r="Y10" s="39"/>
+      <c r="Z10" s="40"/>
+      <c r="AA10" s="41"/>
+      <c r="AB10" s="42"/>
+      <c r="AC10" s="37"/>
+      <c r="AD10" s="43"/>
+      <c r="AE10" s="39"/>
+      <c r="AF10" s="40"/>
+      <c r="AG10" s="41"/>
+      <c r="AH10" s="42"/>
+      <c r="AI10" s="37"/>
+      <c r="AJ10" s="43"/>
+      <c r="AK10" s="39"/>
+      <c r="AL10" s="40"/>
+      <c r="AM10" s="41"/>
+      <c r="AN10" s="42"/>
+      <c r="AO10" s="37"/>
+      <c r="AP10" s="38"/>
+      <c r="AQ10" s="39"/>
+      <c r="AR10" s="40"/>
+      <c r="AS10" s="41"/>
+      <c r="AT10" s="42"/>
+      <c r="AU10" s="37"/>
+      <c r="AV10" s="38"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A11" s="34"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="L11" s="25" t="s">
+    <row r="11" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A11" s="29"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="29"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L11" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M11" s="29"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R11" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S11" s="29"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="33"/>
+      <c r="V11" s="34"/>
+      <c r="W11" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X11" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y11" s="29"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="33"/>
+      <c r="AB11" s="34"/>
+      <c r="AC11" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD11" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE11" s="29"/>
+      <c r="AF11" s="31"/>
+      <c r="AG11" s="33"/>
+      <c r="AH11" s="34"/>
+      <c r="AI11" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ11" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK11" s="29"/>
+      <c r="AL11" s="31"/>
+      <c r="AM11" s="33"/>
+      <c r="AN11" s="34"/>
+      <c r="AO11" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP11" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ11" s="29"/>
+      <c r="AR11" s="31"/>
+      <c r="AS11" s="33"/>
+      <c r="AT11" s="34"/>
+      <c r="AU11" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV11" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A12" s="35"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="26"/>
+    <row r="12" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A12" s="39"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="37"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="39"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="41"/>
+      <c r="V12" s="42"/>
+      <c r="W12" s="37"/>
+      <c r="X12" s="38"/>
+      <c r="Y12" s="39"/>
+      <c r="Z12" s="40"/>
+      <c r="AA12" s="41"/>
+      <c r="AB12" s="42"/>
+      <c r="AC12" s="37"/>
+      <c r="AD12" s="43"/>
+      <c r="AE12" s="39"/>
+      <c r="AF12" s="40"/>
+      <c r="AG12" s="41"/>
+      <c r="AH12" s="42"/>
+      <c r="AI12" s="37"/>
+      <c r="AJ12" s="43"/>
+      <c r="AK12" s="39"/>
+      <c r="AL12" s="40"/>
+      <c r="AM12" s="41"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="37"/>
+      <c r="AP12" s="38"/>
+      <c r="AQ12" s="39"/>
+      <c r="AR12" s="40"/>
+      <c r="AS12" s="41"/>
+      <c r="AT12" s="42"/>
+      <c r="AU12" s="37"/>
+      <c r="AV12" s="38"/>
     </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A13" s="34"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G13" s="34"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="L13" s="25" t="s">
+    <row r="13" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A13" s="29"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="29"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L13" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M13" s="29"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R13" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S13" s="29"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="33"/>
+      <c r="V13" s="34"/>
+      <c r="W13" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X13" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="33"/>
+      <c r="AB13" s="34"/>
+      <c r="AC13" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD13" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE13" s="29"/>
+      <c r="AF13" s="31"/>
+      <c r="AG13" s="33"/>
+      <c r="AH13" s="34"/>
+      <c r="AI13" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ13" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK13" s="29"/>
+      <c r="AL13" s="31"/>
+      <c r="AM13" s="33"/>
+      <c r="AN13" s="34"/>
+      <c r="AO13" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP13" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ13" s="29"/>
+      <c r="AR13" s="31"/>
+      <c r="AS13" s="33"/>
+      <c r="AT13" s="34"/>
+      <c r="AU13" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV13" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A14" s="35"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="26"/>
+    <row r="14" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A14" s="39"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="37"/>
+      <c r="R14" s="38"/>
+      <c r="S14" s="39"/>
+      <c r="T14" s="40"/>
+      <c r="U14" s="41"/>
+      <c r="V14" s="42"/>
+      <c r="W14" s="37"/>
+      <c r="X14" s="38"/>
+      <c r="Y14" s="39"/>
+      <c r="Z14" s="40"/>
+      <c r="AA14" s="41"/>
+      <c r="AB14" s="42"/>
+      <c r="AC14" s="37"/>
+      <c r="AD14" s="43"/>
+      <c r="AE14" s="39"/>
+      <c r="AF14" s="40"/>
+      <c r="AG14" s="41"/>
+      <c r="AH14" s="42"/>
+      <c r="AI14" s="37"/>
+      <c r="AJ14" s="43"/>
+      <c r="AK14" s="39"/>
+      <c r="AL14" s="40"/>
+      <c r="AM14" s="41"/>
+      <c r="AN14" s="42"/>
+      <c r="AO14" s="37"/>
+      <c r="AP14" s="38"/>
+      <c r="AQ14" s="39"/>
+      <c r="AR14" s="40"/>
+      <c r="AS14" s="41"/>
+      <c r="AT14" s="42"/>
+      <c r="AU14" s="37"/>
+      <c r="AV14" s="38"/>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A15" s="34"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="L15" s="25" t="s">
+    <row r="15" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A15" s="29"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="29"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M15" s="29"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S15" s="29"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="33"/>
+      <c r="V15" s="34"/>
+      <c r="W15" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X15" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="31"/>
+      <c r="AA15" s="33"/>
+      <c r="AB15" s="34"/>
+      <c r="AC15" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD15" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE15" s="29"/>
+      <c r="AF15" s="31"/>
+      <c r="AG15" s="33"/>
+      <c r="AH15" s="34"/>
+      <c r="AI15" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ15" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK15" s="29"/>
+      <c r="AL15" s="31"/>
+      <c r="AM15" s="33"/>
+      <c r="AN15" s="34"/>
+      <c r="AO15" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP15" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ15" s="29"/>
+      <c r="AR15" s="31"/>
+      <c r="AS15" s="33"/>
+      <c r="AT15" s="34"/>
+      <c r="AU15" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV15" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A16" s="35"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="26"/>
+    <row r="16" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A16" s="39"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="37"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="39"/>
+      <c r="T16" s="40"/>
+      <c r="U16" s="41"/>
+      <c r="V16" s="42"/>
+      <c r="W16" s="37"/>
+      <c r="X16" s="38"/>
+      <c r="Y16" s="39"/>
+      <c r="Z16" s="40"/>
+      <c r="AA16" s="41"/>
+      <c r="AB16" s="42"/>
+      <c r="AC16" s="37"/>
+      <c r="AD16" s="43"/>
+      <c r="AE16" s="39"/>
+      <c r="AF16" s="40"/>
+      <c r="AG16" s="41"/>
+      <c r="AH16" s="42"/>
+      <c r="AI16" s="37"/>
+      <c r="AJ16" s="43"/>
+      <c r="AK16" s="39"/>
+      <c r="AL16" s="40"/>
+      <c r="AM16" s="41"/>
+      <c r="AN16" s="42"/>
+      <c r="AO16" s="37"/>
+      <c r="AP16" s="38"/>
+      <c r="AQ16" s="39"/>
+      <c r="AR16" s="40"/>
+      <c r="AS16" s="41"/>
+      <c r="AT16" s="42"/>
+      <c r="AU16" s="37"/>
+      <c r="AV16" s="38"/>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A17" s="34"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="L17" s="21" t="s">
+    <row r="17" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A17" s="29"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="29"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="29"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="29"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="33"/>
+      <c r="V17" s="34"/>
+      <c r="W17" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="31"/>
+      <c r="AA17" s="33"/>
+      <c r="AB17" s="34"/>
+      <c r="AC17" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="29"/>
+      <c r="AF17" s="31"/>
+      <c r="AG17" s="33"/>
+      <c r="AH17" s="34"/>
+      <c r="AI17" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ17" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK17" s="29"/>
+      <c r="AL17" s="31"/>
+      <c r="AM17" s="33"/>
+      <c r="AN17" s="34"/>
+      <c r="AO17" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP17" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ17" s="29"/>
+      <c r="AR17" s="31"/>
+      <c r="AS17" s="33"/>
+      <c r="AT17" s="34"/>
+      <c r="AU17" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV17" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A18" s="35"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="22"/>
+    <row r="18" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A18" s="39"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="41"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="37"/>
+      <c r="R18" s="38"/>
+      <c r="S18" s="39"/>
+      <c r="T18" s="40"/>
+      <c r="U18" s="41"/>
+      <c r="V18" s="42"/>
+      <c r="W18" s="37"/>
+      <c r="X18" s="38"/>
+      <c r="Y18" s="39"/>
+      <c r="Z18" s="40"/>
+      <c r="AA18" s="41"/>
+      <c r="AB18" s="42"/>
+      <c r="AC18" s="37"/>
+      <c r="AD18" s="43"/>
+      <c r="AE18" s="39"/>
+      <c r="AF18" s="40"/>
+      <c r="AG18" s="41"/>
+      <c r="AH18" s="42"/>
+      <c r="AI18" s="37"/>
+      <c r="AJ18" s="43"/>
+      <c r="AK18" s="39"/>
+      <c r="AL18" s="40"/>
+      <c r="AM18" s="41"/>
+      <c r="AN18" s="42"/>
+      <c r="AO18" s="37"/>
+      <c r="AP18" s="38"/>
+      <c r="AQ18" s="39"/>
+      <c r="AR18" s="40"/>
+      <c r="AS18" s="41"/>
+      <c r="AT18" s="42"/>
+      <c r="AU18" s="37"/>
+      <c r="AV18" s="38"/>
     </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A19" s="34"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G19" s="34"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="L19" s="21" t="s">
+    <row r="19" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A19" s="29"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19" s="29"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L19" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M19" s="29"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R19" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S19" s="29"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="33"/>
+      <c r="V19" s="34"/>
+      <c r="W19" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X19" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y19" s="29"/>
+      <c r="Z19" s="31"/>
+      <c r="AA19" s="33"/>
+      <c r="AB19" s="34"/>
+      <c r="AC19" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD19" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE19" s="29"/>
+      <c r="AF19" s="31"/>
+      <c r="AG19" s="33"/>
+      <c r="AH19" s="34"/>
+      <c r="AI19" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ19" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK19" s="29"/>
+      <c r="AL19" s="31"/>
+      <c r="AM19" s="33"/>
+      <c r="AN19" s="34"/>
+      <c r="AO19" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP19" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ19" s="29"/>
+      <c r="AR19" s="31"/>
+      <c r="AS19" s="33"/>
+      <c r="AT19" s="34"/>
+      <c r="AU19" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV19" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A20" s="35"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="22"/>
+    <row r="20" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A20" s="39"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="41"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="37"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="39"/>
+      <c r="T20" s="40"/>
+      <c r="U20" s="41"/>
+      <c r="V20" s="42"/>
+      <c r="W20" s="37"/>
+      <c r="X20" s="38"/>
+      <c r="Y20" s="39"/>
+      <c r="Z20" s="40"/>
+      <c r="AA20" s="41"/>
+      <c r="AB20" s="42"/>
+      <c r="AC20" s="37"/>
+      <c r="AD20" s="43"/>
+      <c r="AE20" s="39"/>
+      <c r="AF20" s="40"/>
+      <c r="AG20" s="41"/>
+      <c r="AH20" s="42"/>
+      <c r="AI20" s="37"/>
+      <c r="AJ20" s="43"/>
+      <c r="AK20" s="39"/>
+      <c r="AL20" s="40"/>
+      <c r="AM20" s="41"/>
+      <c r="AN20" s="42"/>
+      <c r="AO20" s="37"/>
+      <c r="AP20" s="38"/>
+      <c r="AQ20" s="39"/>
+      <c r="AR20" s="40"/>
+      <c r="AS20" s="41"/>
+      <c r="AT20" s="42"/>
+      <c r="AU20" s="37"/>
+      <c r="AV20" s="38"/>
     </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A21" s="34"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="34"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="L21" s="21" t="s">
+    <row r="21" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A21" s="29"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="29"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="29"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="29"/>
+      <c r="T21" s="31"/>
+      <c r="U21" s="33"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="29"/>
+      <c r="Z21" s="31"/>
+      <c r="AA21" s="33"/>
+      <c r="AB21" s="34"/>
+      <c r="AC21" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="29"/>
+      <c r="AF21" s="31"/>
+      <c r="AG21" s="33"/>
+      <c r="AH21" s="34"/>
+      <c r="AI21" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ21" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK21" s="29"/>
+      <c r="AL21" s="31"/>
+      <c r="AM21" s="33"/>
+      <c r="AN21" s="34"/>
+      <c r="AO21" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP21" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ21" s="29"/>
+      <c r="AR21" s="31"/>
+      <c r="AS21" s="33"/>
+      <c r="AT21" s="34"/>
+      <c r="AU21" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV21" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A22" s="35"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="22"/>
+    <row r="22" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A22" s="39"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="41"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="37"/>
+      <c r="R22" s="38"/>
+      <c r="S22" s="39"/>
+      <c r="T22" s="40"/>
+      <c r="U22" s="41"/>
+      <c r="V22" s="42"/>
+      <c r="W22" s="37"/>
+      <c r="X22" s="38"/>
+      <c r="Y22" s="39"/>
+      <c r="Z22" s="40"/>
+      <c r="AA22" s="41"/>
+      <c r="AB22" s="42"/>
+      <c r="AC22" s="37"/>
+      <c r="AD22" s="43"/>
+      <c r="AE22" s="39"/>
+      <c r="AF22" s="40"/>
+      <c r="AG22" s="41"/>
+      <c r="AH22" s="42"/>
+      <c r="AI22" s="37"/>
+      <c r="AJ22" s="43"/>
+      <c r="AK22" s="39"/>
+      <c r="AL22" s="40"/>
+      <c r="AM22" s="41"/>
+      <c r="AN22" s="42"/>
+      <c r="AO22" s="37"/>
+      <c r="AP22" s="38"/>
+      <c r="AQ22" s="39"/>
+      <c r="AR22" s="40"/>
+      <c r="AS22" s="41"/>
+      <c r="AT22" s="42"/>
+      <c r="AU22" s="37"/>
+      <c r="AV22" s="38"/>
     </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A23" s="34"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="34"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="24" t="s">
+    <row r="23" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A23" s="29"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="29"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="29"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="29"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="33"/>
+      <c r="V23" s="34"/>
+      <c r="W23" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="29"/>
+      <c r="Z23" s="46"/>
+      <c r="AA23" s="33"/>
+      <c r="AB23" s="34"/>
+      <c r="AC23" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE23" s="29"/>
+      <c r="AF23" s="46"/>
+      <c r="AG23" s="33"/>
+      <c r="AH23" s="34"/>
+      <c r="AI23" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ23" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK23" s="29"/>
+      <c r="AL23" s="31"/>
+      <c r="AM23" s="33"/>
+      <c r="AN23" s="34"/>
+      <c r="AO23" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP23" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ23" s="29"/>
+      <c r="AR23" s="31"/>
+      <c r="AS23" s="33"/>
+      <c r="AT23" s="34"/>
+      <c r="AU23" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV23" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A24" s="35"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="22"/>
+    <row r="24" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A24" s="39"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="41"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="37"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="39"/>
+      <c r="T24" s="40"/>
+      <c r="U24" s="41"/>
+      <c r="V24" s="42"/>
+      <c r="W24" s="37"/>
+      <c r="X24" s="38"/>
+      <c r="Y24" s="39"/>
+      <c r="Z24" s="40"/>
+      <c r="AA24" s="41"/>
+      <c r="AB24" s="42"/>
+      <c r="AC24" s="37"/>
+      <c r="AD24" s="43"/>
+      <c r="AE24" s="39"/>
+      <c r="AF24" s="40"/>
+      <c r="AG24" s="41"/>
+      <c r="AH24" s="42"/>
+      <c r="AI24" s="37"/>
+      <c r="AJ24" s="43"/>
+      <c r="AK24" s="39"/>
+      <c r="AL24" s="40"/>
+      <c r="AM24" s="41"/>
+      <c r="AN24" s="42"/>
+      <c r="AO24" s="37"/>
+      <c r="AP24" s="38"/>
+      <c r="AQ24" s="39"/>
+      <c r="AR24" s="40"/>
+      <c r="AS24" s="41"/>
+      <c r="AT24" s="42"/>
+      <c r="AU24" s="37"/>
+      <c r="AV24" s="38"/>
     </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A25" s="34"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G25" s="34"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="44"/>
-      <c r="K25" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="L25" s="25" t="s">
+    <row r="25" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A25" s="29"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="29"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L25" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M25" s="29"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R25" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S25" s="29"/>
+      <c r="T25" s="31"/>
+      <c r="U25" s="33"/>
+      <c r="V25" s="34"/>
+      <c r="W25" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X25" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y25" s="29"/>
+      <c r="Z25" s="31"/>
+      <c r="AA25" s="33"/>
+      <c r="AB25" s="34"/>
+      <c r="AC25" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD25" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE25" s="29"/>
+      <c r="AF25" s="31"/>
+      <c r="AG25" s="33"/>
+      <c r="AH25" s="34"/>
+      <c r="AI25" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ25" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK25" s="29"/>
+      <c r="AL25" s="31"/>
+      <c r="AM25" s="33"/>
+      <c r="AN25" s="34"/>
+      <c r="AO25" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP25" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ25" s="29"/>
+      <c r="AR25" s="31"/>
+      <c r="AS25" s="33"/>
+      <c r="AT25" s="34"/>
+      <c r="AU25" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV25" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A26" s="35"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="26"/>
+    <row r="26" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A26" s="39"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="41"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="37"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="39"/>
+      <c r="T26" s="40"/>
+      <c r="U26" s="41"/>
+      <c r="V26" s="42"/>
+      <c r="W26" s="37"/>
+      <c r="X26" s="38"/>
+      <c r="Y26" s="39"/>
+      <c r="Z26" s="40"/>
+      <c r="AA26" s="41"/>
+      <c r="AB26" s="42"/>
+      <c r="AC26" s="37"/>
+      <c r="AD26" s="43"/>
+      <c r="AE26" s="39"/>
+      <c r="AF26" s="40"/>
+      <c r="AG26" s="41"/>
+      <c r="AH26" s="42"/>
+      <c r="AI26" s="37"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="39"/>
+      <c r="AL26" s="40"/>
+      <c r="AM26" s="41"/>
+      <c r="AN26" s="42"/>
+      <c r="AO26" s="37"/>
+      <c r="AP26" s="38"/>
+      <c r="AQ26" s="39"/>
+      <c r="AR26" s="40"/>
+      <c r="AS26" s="41"/>
+      <c r="AT26" s="42"/>
+      <c r="AU26" s="37"/>
+      <c r="AV26" s="38"/>
     </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A27" s="34"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="34"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="44"/>
-      <c r="K27" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="L27" s="25" t="s">
+    <row r="27" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A27" s="29"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="29"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="29"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="29"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="34"/>
+      <c r="W27" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y27" s="29"/>
+      <c r="Z27" s="31"/>
+      <c r="AA27" s="33"/>
+      <c r="AB27" s="34"/>
+      <c r="AC27" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD27" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE27" s="29"/>
+      <c r="AF27" s="31"/>
+      <c r="AG27" s="33"/>
+      <c r="AH27" s="34"/>
+      <c r="AI27" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ27" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK27" s="29"/>
+      <c r="AL27" s="31"/>
+      <c r="AM27" s="33"/>
+      <c r="AN27" s="34"/>
+      <c r="AO27" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP27" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ27" s="29"/>
+      <c r="AR27" s="31"/>
+      <c r="AS27" s="33"/>
+      <c r="AT27" s="34"/>
+      <c r="AU27" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV27" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A28" s="35"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="26"/>
+    <row r="28" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A28" s="39"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="43"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="37"/>
+      <c r="R28" s="38"/>
+      <c r="S28" s="39"/>
+      <c r="T28" s="40"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="42"/>
+      <c r="W28" s="37"/>
+      <c r="X28" s="38"/>
+      <c r="Y28" s="39"/>
+      <c r="Z28" s="40"/>
+      <c r="AA28" s="41"/>
+      <c r="AB28" s="42"/>
+      <c r="AC28" s="37"/>
+      <c r="AD28" s="43"/>
+      <c r="AE28" s="39"/>
+      <c r="AF28" s="40"/>
+      <c r="AG28" s="41"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="37"/>
+      <c r="AJ28" s="43"/>
+      <c r="AK28" s="39"/>
+      <c r="AL28" s="40"/>
+      <c r="AM28" s="41"/>
+      <c r="AN28" s="42"/>
+      <c r="AO28" s="37"/>
+      <c r="AP28" s="38"/>
+      <c r="AQ28" s="39"/>
+      <c r="AR28" s="40"/>
+      <c r="AS28" s="41"/>
+      <c r="AT28" s="42"/>
+      <c r="AU28" s="37"/>
+      <c r="AV28" s="38"/>
     </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A29" s="34"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="34"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="44"/>
-      <c r="K29" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="L29" s="25" t="s">
+    <row r="29" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A29" s="29"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="29"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="34"/>
+      <c r="K29" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L29" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M29" s="29"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="34"/>
+      <c r="Q29" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="29"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="33"/>
+      <c r="V29" s="34"/>
+      <c r="W29" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="33"/>
+      <c r="AB29" s="34"/>
+      <c r="AC29" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="29"/>
+      <c r="AF29" s="31"/>
+      <c r="AG29" s="33"/>
+      <c r="AH29" s="34"/>
+      <c r="AI29" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ29" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK29" s="29"/>
+      <c r="AL29" s="31"/>
+      <c r="AM29" s="33"/>
+      <c r="AN29" s="34"/>
+      <c r="AO29" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP29" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ29" s="29"/>
+      <c r="AR29" s="31"/>
+      <c r="AS29" s="33"/>
+      <c r="AT29" s="34"/>
+      <c r="AU29" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV29" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A30" s="35"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="26"/>
+    <row r="30" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A30" s="39"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="37"/>
+      <c r="R30" s="38"/>
+      <c r="S30" s="39"/>
+      <c r="T30" s="40"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="42"/>
+      <c r="W30" s="37"/>
+      <c r="X30" s="38"/>
+      <c r="Y30" s="39"/>
+      <c r="Z30" s="40"/>
+      <c r="AA30" s="41"/>
+      <c r="AB30" s="42"/>
+      <c r="AC30" s="37"/>
+      <c r="AD30" s="43"/>
+      <c r="AE30" s="39"/>
+      <c r="AF30" s="40"/>
+      <c r="AG30" s="41"/>
+      <c r="AH30" s="42"/>
+      <c r="AI30" s="37"/>
+      <c r="AJ30" s="43"/>
+      <c r="AK30" s="39"/>
+      <c r="AL30" s="40"/>
+      <c r="AM30" s="41"/>
+      <c r="AN30" s="42"/>
+      <c r="AO30" s="37"/>
+      <c r="AP30" s="38"/>
+      <c r="AQ30" s="39"/>
+      <c r="AR30" s="40"/>
+      <c r="AS30" s="41"/>
+      <c r="AT30" s="42"/>
+      <c r="AU30" s="37"/>
+      <c r="AV30" s="38"/>
     </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A31" s="34"/>
-      <c r="B31" s="48"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G31" s="34"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="44"/>
-      <c r="K31" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="L31" s="25" t="s">
+    <row r="31" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A31" s="29"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G31" s="29"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L31" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M31" s="29"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R31" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S31" s="29"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="33"/>
+      <c r="V31" s="34"/>
+      <c r="W31" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X31" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y31" s="29"/>
+      <c r="Z31" s="31"/>
+      <c r="AA31" s="33"/>
+      <c r="AB31" s="34"/>
+      <c r="AC31" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD31" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE31" s="29"/>
+      <c r="AF31" s="31"/>
+      <c r="AG31" s="33"/>
+      <c r="AH31" s="34"/>
+      <c r="AI31" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ31" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK31" s="29"/>
+      <c r="AL31" s="31"/>
+      <c r="AM31" s="33"/>
+      <c r="AN31" s="34"/>
+      <c r="AO31" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP31" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ31" s="29"/>
+      <c r="AR31" s="31"/>
+      <c r="AS31" s="33"/>
+      <c r="AT31" s="34"/>
+      <c r="AU31" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV31" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A32" s="35"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="26"/>
+    <row r="32" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A32" s="39"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="39"/>
+      <c r="N32" s="40"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="37"/>
+      <c r="R32" s="38"/>
+      <c r="S32" s="39"/>
+      <c r="T32" s="40"/>
+      <c r="U32" s="41"/>
+      <c r="V32" s="42"/>
+      <c r="W32" s="37"/>
+      <c r="X32" s="38"/>
+      <c r="Y32" s="39"/>
+      <c r="Z32" s="40"/>
+      <c r="AA32" s="41"/>
+      <c r="AB32" s="42"/>
+      <c r="AC32" s="37"/>
+      <c r="AD32" s="43"/>
+      <c r="AE32" s="39"/>
+      <c r="AF32" s="40"/>
+      <c r="AG32" s="41"/>
+      <c r="AH32" s="42"/>
+      <c r="AI32" s="37"/>
+      <c r="AJ32" s="43"/>
+      <c r="AK32" s="39"/>
+      <c r="AL32" s="40"/>
+      <c r="AM32" s="41"/>
+      <c r="AN32" s="42"/>
+      <c r="AO32" s="37"/>
+      <c r="AP32" s="38"/>
+      <c r="AQ32" s="39"/>
+      <c r="AR32" s="40"/>
+      <c r="AS32" s="41"/>
+      <c r="AT32" s="42"/>
+      <c r="AU32" s="37"/>
+      <c r="AV32" s="38"/>
     </row>
-    <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A33" s="34"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="34"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="44"/>
-      <c r="K33" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="L33" s="25" t="s">
+    <row r="33" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A33" s="29"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="29"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M33" s="29"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="34"/>
+      <c r="Q33" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="29"/>
+      <c r="T33" s="31"/>
+      <c r="U33" s="33"/>
+      <c r="V33" s="34"/>
+      <c r="W33" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="29"/>
+      <c r="Z33" s="31"/>
+      <c r="AA33" s="33"/>
+      <c r="AB33" s="34"/>
+      <c r="AC33" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD33" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE33" s="29"/>
+      <c r="AF33" s="31"/>
+      <c r="AG33" s="33"/>
+      <c r="AH33" s="34"/>
+      <c r="AI33" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ33" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK33" s="29"/>
+      <c r="AL33" s="31"/>
+      <c r="AM33" s="33"/>
+      <c r="AN33" s="34"/>
+      <c r="AO33" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP33" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ33" s="29"/>
+      <c r="AR33" s="31"/>
+      <c r="AS33" s="33"/>
+      <c r="AT33" s="34"/>
+      <c r="AU33" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV33" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A34" s="35"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="49"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="26"/>
+    <row r="34" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A34" s="39"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="39"/>
+      <c r="N34" s="40"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="37"/>
+      <c r="R34" s="38"/>
+      <c r="S34" s="39"/>
+      <c r="T34" s="40"/>
+      <c r="U34" s="41"/>
+      <c r="V34" s="42"/>
+      <c r="W34" s="37"/>
+      <c r="X34" s="38"/>
+      <c r="Y34" s="39"/>
+      <c r="Z34" s="40"/>
+      <c r="AA34" s="41"/>
+      <c r="AB34" s="42"/>
+      <c r="AC34" s="37"/>
+      <c r="AD34" s="43"/>
+      <c r="AE34" s="39"/>
+      <c r="AF34" s="40"/>
+      <c r="AG34" s="41"/>
+      <c r="AH34" s="42"/>
+      <c r="AI34" s="37"/>
+      <c r="AJ34" s="43"/>
+      <c r="AK34" s="39"/>
+      <c r="AL34" s="40"/>
+      <c r="AM34" s="41"/>
+      <c r="AN34" s="42"/>
+      <c r="AO34" s="37"/>
+      <c r="AP34" s="38"/>
+      <c r="AQ34" s="39"/>
+      <c r="AR34" s="40"/>
+      <c r="AS34" s="41"/>
+      <c r="AT34" s="42"/>
+      <c r="AU34" s="37"/>
+      <c r="AV34" s="38"/>
     </row>
-    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A35" s="34"/>
-      <c r="B35" s="48"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="34"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="44"/>
-      <c r="K35" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="L35" s="25" t="s">
+    <row r="35" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A35" s="29"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="29"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="34"/>
+      <c r="K35" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M35" s="29"/>
+      <c r="N35" s="31"/>
+      <c r="O35" s="33"/>
+      <c r="P35" s="34"/>
+      <c r="Q35" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="29"/>
+      <c r="T35" s="31"/>
+      <c r="U35" s="33"/>
+      <c r="V35" s="34"/>
+      <c r="W35" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y35" s="29"/>
+      <c r="Z35" s="31"/>
+      <c r="AA35" s="33"/>
+      <c r="AB35" s="34"/>
+      <c r="AC35" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD35" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE35" s="29"/>
+      <c r="AF35" s="31"/>
+      <c r="AG35" s="33"/>
+      <c r="AH35" s="34"/>
+      <c r="AI35" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ35" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK35" s="29"/>
+      <c r="AL35" s="31"/>
+      <c r="AM35" s="33"/>
+      <c r="AN35" s="34"/>
+      <c r="AO35" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP35" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ35" s="29"/>
+      <c r="AR35" s="31"/>
+      <c r="AS35" s="33"/>
+      <c r="AT35" s="34"/>
+      <c r="AU35" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV35" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A36" s="35"/>
-      <c r="B36" s="49"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="26"/>
+    <row r="36" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A36" s="39"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="37"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="39"/>
+      <c r="N36" s="40"/>
+      <c r="O36" s="41"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="37"/>
+      <c r="R36" s="38"/>
+      <c r="S36" s="39"/>
+      <c r="T36" s="40"/>
+      <c r="U36" s="41"/>
+      <c r="V36" s="42"/>
+      <c r="W36" s="37"/>
+      <c r="X36" s="38"/>
+      <c r="Y36" s="39"/>
+      <c r="Z36" s="40"/>
+      <c r="AA36" s="41"/>
+      <c r="AB36" s="42"/>
+      <c r="AC36" s="37"/>
+      <c r="AD36" s="43"/>
+      <c r="AE36" s="39"/>
+      <c r="AF36" s="40"/>
+      <c r="AG36" s="41"/>
+      <c r="AH36" s="42"/>
+      <c r="AI36" s="37"/>
+      <c r="AJ36" s="43"/>
+      <c r="AK36" s="39"/>
+      <c r="AL36" s="40"/>
+      <c r="AM36" s="41"/>
+      <c r="AN36" s="42"/>
+      <c r="AO36" s="37"/>
+      <c r="AP36" s="38"/>
+      <c r="AQ36" s="39"/>
+      <c r="AR36" s="40"/>
+      <c r="AS36" s="41"/>
+      <c r="AT36" s="42"/>
+      <c r="AU36" s="37"/>
+      <c r="AV36" s="38"/>
     </row>
-    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A37" s="34"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="43"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G37" s="34"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="43"/>
-      <c r="J37" s="44"/>
-      <c r="K37" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="L37" s="21" t="s">
+    <row r="37" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A37" s="29"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G37" s="29"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="34"/>
+      <c r="K37" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L37" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M37" s="29"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="34"/>
+      <c r="Q37" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R37" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S37" s="29"/>
+      <c r="T37" s="31"/>
+      <c r="U37" s="33"/>
+      <c r="V37" s="34"/>
+      <c r="W37" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X37" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y37" s="29"/>
+      <c r="Z37" s="31"/>
+      <c r="AA37" s="33"/>
+      <c r="AB37" s="34"/>
+      <c r="AC37" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD37" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE37" s="29"/>
+      <c r="AF37" s="31"/>
+      <c r="AG37" s="33"/>
+      <c r="AH37" s="34"/>
+      <c r="AI37" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ37" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK37" s="29"/>
+      <c r="AL37" s="31"/>
+      <c r="AM37" s="33"/>
+      <c r="AN37" s="34"/>
+      <c r="AO37" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP37" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ37" s="29"/>
+      <c r="AR37" s="31"/>
+      <c r="AS37" s="33"/>
+      <c r="AT37" s="34"/>
+      <c r="AU37" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV37" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A38" s="35"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="22"/>
+    <row r="38" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A38" s="39"/>
+      <c r="B38" s="40"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="37"/>
+      <c r="L38" s="43"/>
+      <c r="M38" s="39"/>
+      <c r="N38" s="40"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="37"/>
+      <c r="R38" s="38"/>
+      <c r="S38" s="39"/>
+      <c r="T38" s="40"/>
+      <c r="U38" s="41"/>
+      <c r="V38" s="42"/>
+      <c r="W38" s="37"/>
+      <c r="X38" s="38"/>
+      <c r="Y38" s="39"/>
+      <c r="Z38" s="40"/>
+      <c r="AA38" s="41"/>
+      <c r="AB38" s="42"/>
+      <c r="AC38" s="37"/>
+      <c r="AD38" s="43"/>
+      <c r="AE38" s="39"/>
+      <c r="AF38" s="40"/>
+      <c r="AG38" s="41"/>
+      <c r="AH38" s="42"/>
+      <c r="AI38" s="37"/>
+      <c r="AJ38" s="43"/>
+      <c r="AK38" s="39"/>
+      <c r="AL38" s="40"/>
+      <c r="AM38" s="41"/>
+      <c r="AN38" s="42"/>
+      <c r="AO38" s="37"/>
+      <c r="AP38" s="38"/>
+      <c r="AQ38" s="39"/>
+      <c r="AR38" s="40"/>
+      <c r="AS38" s="41"/>
+      <c r="AT38" s="42"/>
+      <c r="AU38" s="37"/>
+      <c r="AV38" s="38"/>
     </row>
-    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A39" s="34"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G39" s="34"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="43"/>
-      <c r="J39" s="44"/>
-      <c r="K39" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="L39" s="21" t="s">
+    <row r="39" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A39" s="29"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G39" s="29"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="34"/>
+      <c r="K39" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L39" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M39" s="29"/>
+      <c r="N39" s="31"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="34"/>
+      <c r="Q39" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R39" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S39" s="29"/>
+      <c r="T39" s="31"/>
+      <c r="U39" s="33"/>
+      <c r="V39" s="34"/>
+      <c r="W39" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X39" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y39" s="29"/>
+      <c r="Z39" s="31"/>
+      <c r="AA39" s="33"/>
+      <c r="AB39" s="34"/>
+      <c r="AC39" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD39" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE39" s="29"/>
+      <c r="AF39" s="31"/>
+      <c r="AG39" s="33"/>
+      <c r="AH39" s="34"/>
+      <c r="AI39" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ39" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK39" s="29"/>
+      <c r="AL39" s="31"/>
+      <c r="AM39" s="33"/>
+      <c r="AN39" s="34"/>
+      <c r="AO39" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP39" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ39" s="29"/>
+      <c r="AR39" s="31"/>
+      <c r="AS39" s="33"/>
+      <c r="AT39" s="34"/>
+      <c r="AU39" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV39" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A40" s="35"/>
-      <c r="B40" s="38"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="46"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="46"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="22"/>
+    <row r="40" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A40" s="39"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="37"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="39"/>
+      <c r="N40" s="40"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="42"/>
+      <c r="Q40" s="37"/>
+      <c r="R40" s="38"/>
+      <c r="S40" s="39"/>
+      <c r="T40" s="40"/>
+      <c r="U40" s="41"/>
+      <c r="V40" s="42"/>
+      <c r="W40" s="37"/>
+      <c r="X40" s="38"/>
+      <c r="Y40" s="39"/>
+      <c r="Z40" s="40"/>
+      <c r="AA40" s="41"/>
+      <c r="AB40" s="42"/>
+      <c r="AC40" s="37"/>
+      <c r="AD40" s="43"/>
+      <c r="AE40" s="39"/>
+      <c r="AF40" s="40"/>
+      <c r="AG40" s="41"/>
+      <c r="AH40" s="42"/>
+      <c r="AI40" s="37"/>
+      <c r="AJ40" s="43"/>
+      <c r="AK40" s="39"/>
+      <c r="AL40" s="40"/>
+      <c r="AM40" s="41"/>
+      <c r="AN40" s="42"/>
+      <c r="AO40" s="37"/>
+      <c r="AP40" s="38"/>
+      <c r="AQ40" s="39"/>
+      <c r="AR40" s="40"/>
+      <c r="AS40" s="41"/>
+      <c r="AT40" s="42"/>
+      <c r="AU40" s="37"/>
+      <c r="AV40" s="38"/>
     </row>
-    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A41" s="34"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="43"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G41" s="34"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="44"/>
-      <c r="K41" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="L41" s="21" t="s">
+    <row r="41" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A41" s="29"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="29"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="34"/>
+      <c r="K41" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L41" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M41" s="29"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="33"/>
+      <c r="P41" s="34"/>
+      <c r="Q41" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R41" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S41" s="29"/>
+      <c r="T41" s="31"/>
+      <c r="U41" s="33"/>
+      <c r="V41" s="34"/>
+      <c r="W41" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y41" s="29"/>
+      <c r="Z41" s="31"/>
+      <c r="AA41" s="33"/>
+      <c r="AB41" s="34"/>
+      <c r="AC41" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE41" s="29"/>
+      <c r="AF41" s="31"/>
+      <c r="AG41" s="33"/>
+      <c r="AH41" s="34"/>
+      <c r="AI41" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ41" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK41" s="29"/>
+      <c r="AL41" s="31"/>
+      <c r="AM41" s="33"/>
+      <c r="AN41" s="34"/>
+      <c r="AO41" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP41" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ41" s="29"/>
+      <c r="AR41" s="31"/>
+      <c r="AS41" s="33"/>
+      <c r="AT41" s="34"/>
+      <c r="AU41" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV41" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A42" s="35"/>
-      <c r="B42" s="38"/>
-      <c r="C42" s="45"/>
-      <c r="D42" s="46"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="46"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="22"/>
+    <row r="42" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A42" s="39"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="39"/>
+      <c r="H42" s="40"/>
+      <c r="I42" s="41"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="37"/>
+      <c r="L42" s="43"/>
+      <c r="M42" s="39"/>
+      <c r="N42" s="40"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="37"/>
+      <c r="R42" s="38"/>
+      <c r="S42" s="39"/>
+      <c r="T42" s="40"/>
+      <c r="U42" s="41"/>
+      <c r="V42" s="42"/>
+      <c r="W42" s="37"/>
+      <c r="X42" s="38"/>
+      <c r="Y42" s="39"/>
+      <c r="Z42" s="40"/>
+      <c r="AA42" s="41"/>
+      <c r="AB42" s="42"/>
+      <c r="AC42" s="37"/>
+      <c r="AD42" s="43"/>
+      <c r="AE42" s="39"/>
+      <c r="AF42" s="40"/>
+      <c r="AG42" s="41"/>
+      <c r="AH42" s="42"/>
+      <c r="AI42" s="37"/>
+      <c r="AJ42" s="43"/>
+      <c r="AK42" s="39"/>
+      <c r="AL42" s="40"/>
+      <c r="AM42" s="41"/>
+      <c r="AN42" s="42"/>
+      <c r="AO42" s="37"/>
+      <c r="AP42" s="38"/>
+      <c r="AQ42" s="39"/>
+      <c r="AR42" s="40"/>
+      <c r="AS42" s="41"/>
+      <c r="AT42" s="42"/>
+      <c r="AU42" s="37"/>
+      <c r="AV42" s="38"/>
     </row>
-    <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A43" s="34"/>
-      <c r="B43" s="47"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="G43" s="34"/>
-      <c r="H43" s="47"/>
-      <c r="I43" s="43"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="L43" s="24" t="s">
+    <row r="43" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A43" s="29"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="29"/>
+      <c r="H43" s="46"/>
+      <c r="I43" s="33"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="L43" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="M43" s="29"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="33"/>
+      <c r="P43" s="34"/>
+      <c r="Q43" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R43" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S43" s="29"/>
+      <c r="T43" s="31"/>
+      <c r="U43" s="33"/>
+      <c r="V43" s="34"/>
+      <c r="W43" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y43" s="29"/>
+      <c r="Z43" s="46"/>
+      <c r="AA43" s="33"/>
+      <c r="AB43" s="34"/>
+      <c r="AC43" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="29"/>
+      <c r="AF43" s="46"/>
+      <c r="AG43" s="33"/>
+      <c r="AH43" s="34"/>
+      <c r="AI43" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ43" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK43" s="29"/>
+      <c r="AL43" s="31"/>
+      <c r="AM43" s="33"/>
+      <c r="AN43" s="34"/>
+      <c r="AO43" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP43" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ43" s="29"/>
+      <c r="AR43" s="31"/>
+      <c r="AS43" s="33"/>
+      <c r="AT43" s="34"/>
+      <c r="AU43" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV43" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A44" s="35"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="46"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="22"/>
+    <row r="44" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A44" s="39"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="39"/>
+      <c r="H44" s="40"/>
+      <c r="I44" s="41"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="37"/>
+      <c r="L44" s="43"/>
+      <c r="M44" s="39"/>
+      <c r="N44" s="40"/>
+      <c r="O44" s="41"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="37"/>
+      <c r="R44" s="38"/>
+      <c r="S44" s="39"/>
+      <c r="T44" s="40"/>
+      <c r="U44" s="41"/>
+      <c r="V44" s="42"/>
+      <c r="W44" s="37"/>
+      <c r="X44" s="38"/>
+      <c r="Y44" s="39"/>
+      <c r="Z44" s="40"/>
+      <c r="AA44" s="41"/>
+      <c r="AB44" s="42"/>
+      <c r="AC44" s="37"/>
+      <c r="AD44" s="43"/>
+      <c r="AE44" s="39"/>
+      <c r="AF44" s="40"/>
+      <c r="AG44" s="41"/>
+      <c r="AH44" s="42"/>
+      <c r="AI44" s="37"/>
+      <c r="AJ44" s="43"/>
+      <c r="AK44" s="39"/>
+      <c r="AL44" s="40"/>
+      <c r="AM44" s="41"/>
+      <c r="AN44" s="42"/>
+      <c r="AO44" s="37"/>
+      <c r="AP44" s="38"/>
+      <c r="AQ44" s="39"/>
+      <c r="AR44" s="40"/>
+      <c r="AS44" s="41"/>
+      <c r="AT44" s="42"/>
+      <c r="AU44" s="37"/>
+      <c r="AV44" s="38"/>
     </row>
-    <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A45" s="34"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G45" s="34"/>
-      <c r="H45" s="36"/>
-      <c r="I45" s="43"/>
-      <c r="J45" s="44"/>
-      <c r="K45" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="21" t="s">
+    <row r="45" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A45" s="29"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="29"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="33"/>
+      <c r="J45" s="34"/>
+      <c r="K45" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="29"/>
+      <c r="N45" s="31"/>
+      <c r="O45" s="33"/>
+      <c r="P45" s="34"/>
+      <c r="Q45" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R45" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S45" s="29"/>
+      <c r="T45" s="31"/>
+      <c r="U45" s="33"/>
+      <c r="V45" s="34"/>
+      <c r="W45" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X45" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y45" s="29"/>
+      <c r="Z45" s="31"/>
+      <c r="AA45" s="33"/>
+      <c r="AB45" s="34"/>
+      <c r="AC45" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD45" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE45" s="29"/>
+      <c r="AF45" s="31"/>
+      <c r="AG45" s="33"/>
+      <c r="AH45" s="34"/>
+      <c r="AI45" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ45" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK45" s="29"/>
+      <c r="AL45" s="31"/>
+      <c r="AM45" s="33"/>
+      <c r="AN45" s="34"/>
+      <c r="AO45" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP45" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ45" s="29"/>
+      <c r="AR45" s="31"/>
+      <c r="AS45" s="33"/>
+      <c r="AT45" s="34"/>
+      <c r="AU45" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV45" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A46" s="35"/>
-      <c r="B46" s="38"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="46"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="22"/>
+    <row r="46" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A46" s="39"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="42"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="39"/>
+      <c r="H46" s="40"/>
+      <c r="I46" s="41"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="37"/>
+      <c r="L46" s="43"/>
+      <c r="M46" s="39"/>
+      <c r="N46" s="40"/>
+      <c r="O46" s="41"/>
+      <c r="P46" s="42"/>
+      <c r="Q46" s="37"/>
+      <c r="R46" s="38"/>
+      <c r="S46" s="39"/>
+      <c r="T46" s="40"/>
+      <c r="U46" s="41"/>
+      <c r="V46" s="42"/>
+      <c r="W46" s="37"/>
+      <c r="X46" s="38"/>
+      <c r="Y46" s="39"/>
+      <c r="Z46" s="40"/>
+      <c r="AA46" s="41"/>
+      <c r="AB46" s="42"/>
+      <c r="AC46" s="37"/>
+      <c r="AD46" s="43"/>
+      <c r="AE46" s="39"/>
+      <c r="AF46" s="40"/>
+      <c r="AG46" s="41"/>
+      <c r="AH46" s="42"/>
+      <c r="AI46" s="37"/>
+      <c r="AJ46" s="43"/>
+      <c r="AK46" s="39"/>
+      <c r="AL46" s="40"/>
+      <c r="AM46" s="41"/>
+      <c r="AN46" s="42"/>
+      <c r="AO46" s="37"/>
+      <c r="AP46" s="38"/>
+      <c r="AQ46" s="39"/>
+      <c r="AR46" s="40"/>
+      <c r="AS46" s="41"/>
+      <c r="AT46" s="42"/>
+      <c r="AU46" s="37"/>
+      <c r="AV46" s="38"/>
     </row>
-    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A47" s="34"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="43"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G47" s="34"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="43"/>
-      <c r="J47" s="44"/>
-      <c r="K47" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="L47" s="21" t="s">
+    <row r="47" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A47" s="29"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="29"/>
+      <c r="H47" s="31"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="34"/>
+      <c r="K47" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="29"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="33"/>
+      <c r="P47" s="34"/>
+      <c r="Q47" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R47" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S47" s="29"/>
+      <c r="T47" s="31"/>
+      <c r="U47" s="33"/>
+      <c r="V47" s="34"/>
+      <c r="W47" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y47" s="29"/>
+      <c r="Z47" s="31"/>
+      <c r="AA47" s="33"/>
+      <c r="AB47" s="34"/>
+      <c r="AC47" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="29"/>
+      <c r="AF47" s="31"/>
+      <c r="AG47" s="33"/>
+      <c r="AH47" s="34"/>
+      <c r="AI47" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ47" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK47" s="29"/>
+      <c r="AL47" s="31"/>
+      <c r="AM47" s="33"/>
+      <c r="AN47" s="34"/>
+      <c r="AO47" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP47" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ47" s="29"/>
+      <c r="AR47" s="31"/>
+      <c r="AS47" s="33"/>
+      <c r="AT47" s="34"/>
+      <c r="AU47" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV47" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A48" s="35"/>
-      <c r="B48" s="38"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="35"/>
-      <c r="H48" s="38"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="46"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="22"/>
+    <row r="48" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A48" s="39"/>
+      <c r="B48" s="40"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="39"/>
+      <c r="H48" s="40"/>
+      <c r="I48" s="41"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="37"/>
+      <c r="L48" s="43"/>
+      <c r="M48" s="39"/>
+      <c r="N48" s="40"/>
+      <c r="O48" s="41"/>
+      <c r="P48" s="42"/>
+      <c r="Q48" s="37"/>
+      <c r="R48" s="38"/>
+      <c r="S48" s="39"/>
+      <c r="T48" s="40"/>
+      <c r="U48" s="41"/>
+      <c r="V48" s="42"/>
+      <c r="W48" s="37"/>
+      <c r="X48" s="38"/>
+      <c r="Y48" s="39"/>
+      <c r="Z48" s="40"/>
+      <c r="AA48" s="41"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="37"/>
+      <c r="AD48" s="43"/>
+      <c r="AE48" s="39"/>
+      <c r="AF48" s="40"/>
+      <c r="AG48" s="41"/>
+      <c r="AH48" s="42"/>
+      <c r="AI48" s="37"/>
+      <c r="AJ48" s="43"/>
+      <c r="AK48" s="39"/>
+      <c r="AL48" s="40"/>
+      <c r="AM48" s="41"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="37"/>
+      <c r="AP48" s="38"/>
+      <c r="AQ48" s="39"/>
+      <c r="AR48" s="40"/>
+      <c r="AS48" s="41"/>
+      <c r="AT48" s="42"/>
+      <c r="AU48" s="37"/>
+      <c r="AV48" s="38"/>
     </row>
-    <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A49" s="34"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="44"/>
-      <c r="E49" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G49" s="34"/>
-      <c r="H49" s="36"/>
-      <c r="I49" s="43"/>
-      <c r="J49" s="44"/>
-      <c r="K49" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="L49" s="21" t="s">
+    <row r="49" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A49" s="29"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="29"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="33"/>
+      <c r="J49" s="34"/>
+      <c r="K49" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L49" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M49" s="29"/>
+      <c r="N49" s="31"/>
+      <c r="O49" s="33"/>
+      <c r="P49" s="34"/>
+      <c r="Q49" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R49" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S49" s="29"/>
+      <c r="T49" s="31"/>
+      <c r="U49" s="33"/>
+      <c r="V49" s="34"/>
+      <c r="W49" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y49" s="29"/>
+      <c r="Z49" s="31"/>
+      <c r="AA49" s="33"/>
+      <c r="AB49" s="34"/>
+      <c r="AC49" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD49" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE49" s="29"/>
+      <c r="AF49" s="31"/>
+      <c r="AG49" s="33"/>
+      <c r="AH49" s="34"/>
+      <c r="AI49" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ49" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK49" s="29"/>
+      <c r="AL49" s="31"/>
+      <c r="AM49" s="33"/>
+      <c r="AN49" s="34"/>
+      <c r="AO49" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP49" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ49" s="29"/>
+      <c r="AR49" s="31"/>
+      <c r="AS49" s="33"/>
+      <c r="AT49" s="34"/>
+      <c r="AU49" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV49" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A50" s="35"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="28"/>
-      <c r="L50" s="22"/>
+    <row r="50" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A50" s="39"/>
+      <c r="B50" s="40"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="40"/>
+      <c r="I50" s="41"/>
+      <c r="J50" s="42"/>
+      <c r="K50" s="37"/>
+      <c r="L50" s="43"/>
+      <c r="M50" s="39"/>
+      <c r="N50" s="40"/>
+      <c r="O50" s="41"/>
+      <c r="P50" s="42"/>
+      <c r="Q50" s="37"/>
+      <c r="R50" s="38"/>
+      <c r="S50" s="39"/>
+      <c r="T50" s="40"/>
+      <c r="U50" s="41"/>
+      <c r="V50" s="42"/>
+      <c r="W50" s="37"/>
+      <c r="X50" s="38"/>
+      <c r="Y50" s="39"/>
+      <c r="Z50" s="40"/>
+      <c r="AA50" s="41"/>
+      <c r="AB50" s="42"/>
+      <c r="AC50" s="37"/>
+      <c r="AD50" s="43"/>
+      <c r="AE50" s="39"/>
+      <c r="AF50" s="40"/>
+      <c r="AG50" s="41"/>
+      <c r="AH50" s="42"/>
+      <c r="AI50" s="37"/>
+      <c r="AJ50" s="43"/>
+      <c r="AK50" s="39"/>
+      <c r="AL50" s="40"/>
+      <c r="AM50" s="41"/>
+      <c r="AN50" s="42"/>
+      <c r="AO50" s="37"/>
+      <c r="AP50" s="38"/>
+      <c r="AQ50" s="39"/>
+      <c r="AR50" s="40"/>
+      <c r="AS50" s="41"/>
+      <c r="AT50" s="42"/>
+      <c r="AU50" s="37"/>
+      <c r="AV50" s="38"/>
     </row>
-    <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A51" s="34"/>
-      <c r="B51" s="36"/>
-      <c r="C51" s="43"/>
-      <c r="D51" s="44"/>
-      <c r="E51" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G51" s="34"/>
-      <c r="H51" s="36"/>
-      <c r="I51" s="43"/>
-      <c r="J51" s="44"/>
-      <c r="K51" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="L51" s="21" t="s">
+    <row r="51" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A51" s="29"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F51" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G51" s="29"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="33"/>
+      <c r="J51" s="34"/>
+      <c r="K51" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L51" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M51" s="29"/>
+      <c r="N51" s="31"/>
+      <c r="O51" s="33"/>
+      <c r="P51" s="34"/>
+      <c r="Q51" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R51" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S51" s="29"/>
+      <c r="T51" s="31"/>
+      <c r="U51" s="33"/>
+      <c r="V51" s="34"/>
+      <c r="W51" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X51" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y51" s="29"/>
+      <c r="Z51" s="31"/>
+      <c r="AA51" s="33"/>
+      <c r="AB51" s="34"/>
+      <c r="AC51" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD51" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE51" s="29"/>
+      <c r="AF51" s="31"/>
+      <c r="AG51" s="33"/>
+      <c r="AH51" s="34"/>
+      <c r="AI51" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ51" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK51" s="29"/>
+      <c r="AL51" s="31"/>
+      <c r="AM51" s="33"/>
+      <c r="AN51" s="34"/>
+      <c r="AO51" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP51" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ51" s="29"/>
+      <c r="AR51" s="31"/>
+      <c r="AS51" s="33"/>
+      <c r="AT51" s="34"/>
+      <c r="AU51" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV51" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A52" s="35"/>
-      <c r="B52" s="38"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="38"/>
-      <c r="I52" s="45"/>
-      <c r="J52" s="46"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="22"/>
+    <row r="52" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A52" s="39"/>
+      <c r="B52" s="40"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="42"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="40"/>
+      <c r="I52" s="41"/>
+      <c r="J52" s="42"/>
+      <c r="K52" s="37"/>
+      <c r="L52" s="43"/>
+      <c r="M52" s="39"/>
+      <c r="N52" s="40"/>
+      <c r="O52" s="41"/>
+      <c r="P52" s="42"/>
+      <c r="Q52" s="37"/>
+      <c r="R52" s="38"/>
+      <c r="S52" s="39"/>
+      <c r="T52" s="40"/>
+      <c r="U52" s="41"/>
+      <c r="V52" s="42"/>
+      <c r="W52" s="37"/>
+      <c r="X52" s="38"/>
+      <c r="Y52" s="39"/>
+      <c r="Z52" s="40"/>
+      <c r="AA52" s="41"/>
+      <c r="AB52" s="42"/>
+      <c r="AC52" s="37"/>
+      <c r="AD52" s="43"/>
+      <c r="AE52" s="39"/>
+      <c r="AF52" s="40"/>
+      <c r="AG52" s="41"/>
+      <c r="AH52" s="42"/>
+      <c r="AI52" s="37"/>
+      <c r="AJ52" s="43"/>
+      <c r="AK52" s="39"/>
+      <c r="AL52" s="40"/>
+      <c r="AM52" s="41"/>
+      <c r="AN52" s="42"/>
+      <c r="AO52" s="37"/>
+      <c r="AP52" s="38"/>
+      <c r="AQ52" s="39"/>
+      <c r="AR52" s="40"/>
+      <c r="AS52" s="41"/>
+      <c r="AT52" s="42"/>
+      <c r="AU52" s="37"/>
+      <c r="AV52" s="38"/>
     </row>
-    <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A53" s="34"/>
-      <c r="B53" s="36"/>
-      <c r="C53" s="43"/>
-      <c r="D53" s="44"/>
-      <c r="E53" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G53" s="34"/>
-      <c r="H53" s="36"/>
-      <c r="I53" s="43"/>
-      <c r="J53" s="44"/>
-      <c r="K53" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="L53" s="21" t="s">
+    <row r="53" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A53" s="29"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F53" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G53" s="29"/>
+      <c r="H53" s="31"/>
+      <c r="I53" s="33"/>
+      <c r="J53" s="34"/>
+      <c r="K53" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L53" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M53" s="29"/>
+      <c r="N53" s="31"/>
+      <c r="O53" s="33"/>
+      <c r="P53" s="34"/>
+      <c r="Q53" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R53" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S53" s="29"/>
+      <c r="T53" s="31"/>
+      <c r="U53" s="33"/>
+      <c r="V53" s="34"/>
+      <c r="W53" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X53" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y53" s="29"/>
+      <c r="Z53" s="31"/>
+      <c r="AA53" s="33"/>
+      <c r="AB53" s="34"/>
+      <c r="AC53" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD53" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE53" s="29"/>
+      <c r="AF53" s="31"/>
+      <c r="AG53" s="33"/>
+      <c r="AH53" s="34"/>
+      <c r="AI53" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ53" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK53" s="29"/>
+      <c r="AL53" s="31"/>
+      <c r="AM53" s="33"/>
+      <c r="AN53" s="34"/>
+      <c r="AO53" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP53" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ53" s="29"/>
+      <c r="AR53" s="31"/>
+      <c r="AS53" s="33"/>
+      <c r="AT53" s="34"/>
+      <c r="AU53" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV53" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A54" s="35"/>
-      <c r="B54" s="38"/>
-      <c r="C54" s="45"/>
-      <c r="D54" s="46"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="38"/>
-      <c r="I54" s="45"/>
-      <c r="J54" s="46"/>
-      <c r="K54" s="28"/>
-      <c r="L54" s="22"/>
+    <row r="54" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A54" s="39"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="37"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="39"/>
+      <c r="H54" s="40"/>
+      <c r="I54" s="41"/>
+      <c r="J54" s="42"/>
+      <c r="K54" s="37"/>
+      <c r="L54" s="43"/>
+      <c r="M54" s="39"/>
+      <c r="N54" s="40"/>
+      <c r="O54" s="41"/>
+      <c r="P54" s="42"/>
+      <c r="Q54" s="37"/>
+      <c r="R54" s="38"/>
+      <c r="S54" s="39"/>
+      <c r="T54" s="40"/>
+      <c r="U54" s="41"/>
+      <c r="V54" s="42"/>
+      <c r="W54" s="37"/>
+      <c r="X54" s="38"/>
+      <c r="Y54" s="39"/>
+      <c r="Z54" s="40"/>
+      <c r="AA54" s="41"/>
+      <c r="AB54" s="42"/>
+      <c r="AC54" s="37"/>
+      <c r="AD54" s="43"/>
+      <c r="AE54" s="39"/>
+      <c r="AF54" s="40"/>
+      <c r="AG54" s="41"/>
+      <c r="AH54" s="42"/>
+      <c r="AI54" s="37"/>
+      <c r="AJ54" s="43"/>
+      <c r="AK54" s="39"/>
+      <c r="AL54" s="40"/>
+      <c r="AM54" s="41"/>
+      <c r="AN54" s="42"/>
+      <c r="AO54" s="37"/>
+      <c r="AP54" s="38"/>
+      <c r="AQ54" s="39"/>
+      <c r="AR54" s="40"/>
+      <c r="AS54" s="41"/>
+      <c r="AT54" s="42"/>
+      <c r="AU54" s="37"/>
+      <c r="AV54" s="38"/>
     </row>
-    <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A55" s="34"/>
-      <c r="B55" s="36"/>
-      <c r="C55" s="39"/>
-      <c r="D55" s="40"/>
-      <c r="E55" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G55" s="34"/>
-      <c r="H55" s="36"/>
-      <c r="I55" s="39"/>
-      <c r="J55" s="40"/>
-      <c r="K55" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="L55" s="21" t="s">
+    <row r="55" spans="1:48" x14ac:dyDescent="0.1">
+      <c r="A55" s="29"/>
+      <c r="B55" s="31"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F55" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G55" s="29"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="33"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="L55" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="M55" s="29"/>
+      <c r="N55" s="31"/>
+      <c r="O55" s="33"/>
+      <c r="P55" s="34"/>
+      <c r="Q55" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="R55" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="S55" s="29"/>
+      <c r="T55" s="31"/>
+      <c r="U55" s="33"/>
+      <c r="V55" s="34"/>
+      <c r="W55" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="X55" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y55" s="29"/>
+      <c r="Z55" s="31"/>
+      <c r="AA55" s="33"/>
+      <c r="AB55" s="34"/>
+      <c r="AC55" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD55" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE55" s="29"/>
+      <c r="AF55" s="31"/>
+      <c r="AG55" s="33"/>
+      <c r="AH55" s="34"/>
+      <c r="AI55" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ55" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK55" s="29"/>
+      <c r="AL55" s="31"/>
+      <c r="AM55" s="33"/>
+      <c r="AN55" s="34"/>
+      <c r="AO55" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP55" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ55" s="29"/>
+      <c r="AR55" s="31"/>
+      <c r="AS55" s="33"/>
+      <c r="AT55" s="34"/>
+      <c r="AU55" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV55" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="35"/>
-      <c r="B56" s="37"/>
-      <c r="C56" s="41"/>
-      <c r="D56" s="42"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="37"/>
-      <c r="I56" s="41"/>
-      <c r="J56" s="42"/>
-      <c r="K56" s="29"/>
-      <c r="L56" s="23"/>
+    <row r="56" spans="1:48" ht="14.25" thickBot="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="30"/>
+      <c r="B56" s="32"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="35"/>
+      <c r="J56" s="36"/>
+      <c r="K56" s="24"/>
+      <c r="L56" s="28"/>
+      <c r="M56" s="30"/>
+      <c r="N56" s="32"/>
+      <c r="O56" s="35"/>
+      <c r="P56" s="36"/>
+      <c r="Q56" s="24"/>
+      <c r="R56" s="26"/>
+      <c r="S56" s="30"/>
+      <c r="T56" s="32"/>
+      <c r="U56" s="35"/>
+      <c r="V56" s="36"/>
+      <c r="W56" s="24"/>
+      <c r="X56" s="26"/>
+      <c r="Y56" s="30"/>
+      <c r="Z56" s="32"/>
+      <c r="AA56" s="35"/>
+      <c r="AB56" s="36"/>
+      <c r="AC56" s="24"/>
+      <c r="AD56" s="28"/>
+      <c r="AE56" s="30"/>
+      <c r="AF56" s="32"/>
+      <c r="AG56" s="35"/>
+      <c r="AH56" s="36"/>
+      <c r="AI56" s="24"/>
+      <c r="AJ56" s="28"/>
+      <c r="AK56" s="30"/>
+      <c r="AL56" s="32"/>
+      <c r="AM56" s="35"/>
+      <c r="AN56" s="36"/>
+      <c r="AO56" s="24"/>
+      <c r="AP56" s="26"/>
+      <c r="AQ56" s="30"/>
+      <c r="AR56" s="32"/>
+      <c r="AS56" s="35"/>
+      <c r="AT56" s="36"/>
+      <c r="AU56" s="24"/>
+      <c r="AV56" s="26"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.1">
+    <row r="57" spans="1:48" x14ac:dyDescent="0.1">
       <c r="A57" s="11"/>
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
@@ -4120,10 +9193,45 @@
       <c r="J57" s="11"/>
       <c r="K57" s="12"/>
       <c r="L57" s="12"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="11"/>
+      <c r="O57" s="11"/>
+      <c r="P57" s="11"/>
+      <c r="Q57" s="12"/>
+      <c r="R57" s="12"/>
+      <c r="S57" s="11"/>
+      <c r="T57" s="11"/>
+      <c r="U57" s="11"/>
+      <c r="V57" s="11"/>
+      <c r="W57" s="12"/>
+      <c r="X57" s="12"/>
+      <c r="Y57" s="11"/>
+      <c r="Z57" s="11"/>
+      <c r="AA57" s="11"/>
+      <c r="AB57" s="11"/>
+      <c r="AC57" s="12"/>
+      <c r="AD57" s="12"/>
+      <c r="AE57" s="11"/>
+      <c r="AF57" s="11"/>
+      <c r="AG57" s="11"/>
+      <c r="AH57" s="11"/>
+      <c r="AI57" s="12"/>
+      <c r="AJ57" s="12"/>
+      <c r="AK57" s="11"/>
+      <c r="AL57" s="11"/>
+      <c r="AM57" s="11"/>
+      <c r="AN57" s="11"/>
+      <c r="AO57" s="12"/>
+      <c r="AP57" s="12"/>
+      <c r="AQ57" s="11"/>
+      <c r="AR57" s="11"/>
+      <c r="AS57" s="11"/>
+      <c r="AT57" s="11"/>
+      <c r="AU57" s="12"/>
+      <c r="AV57" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="258">
-    <mergeCell ref="B21:B22"/>
+  <mergeCells count="1032">
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="H21:H22"/>
@@ -4140,6 +9248,33 @@
     <mergeCell ref="C23:D24"/>
     <mergeCell ref="I23:J24"/>
     <mergeCell ref="E23:E24"/>
+    <mergeCell ref="I51:J52"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="C43:D44"/>
+    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="I53:J54"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="K55:K56"/>
+    <mergeCell ref="I55:J56"/>
+    <mergeCell ref="G53:G54"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="K53:K54"/>
     <mergeCell ref="C35:D36"/>
     <mergeCell ref="C37:D38"/>
     <mergeCell ref="C39:D40"/>
@@ -4160,39 +9295,7 @@
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="K15:K16"/>
     <mergeCell ref="C15:D16"/>
-    <mergeCell ref="I15:J16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="I53:J54"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="K49:K50"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="K55:K56"/>
-    <mergeCell ref="I55:J56"/>
-    <mergeCell ref="G53:G54"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="K53:K54"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="K43:K44"/>
-    <mergeCell ref="I43:J44"/>
-    <mergeCell ref="I45:J46"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="C43:D44"/>
-    <mergeCell ref="C45:D46"/>
-    <mergeCell ref="K41:K42"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="I47:J48"/>
-    <mergeCell ref="I49:J50"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="K45:K46"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="K51:K52"/>
-    <mergeCell ref="I51:J52"/>
+    <mergeCell ref="C17:D18"/>
     <mergeCell ref="I7:J8"/>
     <mergeCell ref="I9:J10"/>
     <mergeCell ref="I25:J26"/>
@@ -4211,6 +9314,14 @@
     <mergeCell ref="G19:G20"/>
     <mergeCell ref="H19:H20"/>
     <mergeCell ref="I19:J20"/>
+    <mergeCell ref="I15:J16"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I35:J36"/>
+    <mergeCell ref="I37:J38"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="G37:G38"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="G31:G32"/>
     <mergeCell ref="H31:H32"/>
@@ -4226,30 +9337,6 @@
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="K17:K18"/>
     <mergeCell ref="K19:K20"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I35:J36"/>
-    <mergeCell ref="I37:J38"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="G37:G38"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
@@ -4267,19 +9354,23 @@
     <mergeCell ref="C7:D8"/>
     <mergeCell ref="C9:D10"/>
     <mergeCell ref="C11:D12"/>
-    <mergeCell ref="C17:D18"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="F19:F20"/>
     <mergeCell ref="C19:D20"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="F17:F18"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="F43:F44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="F45:F46"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="A25:A26"/>
@@ -4295,18 +9386,6 @@
     <mergeCell ref="F35:F36"/>
     <mergeCell ref="F37:F38"/>
     <mergeCell ref="F39:F40"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="C47:D48"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="E49:E50"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="B55:B56"/>
     <mergeCell ref="F55:F56"/>
@@ -4319,6 +9398,18 @@
     <mergeCell ref="C55:D56"/>
     <mergeCell ref="C51:D52"/>
     <mergeCell ref="C53:D54"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="C47:D48"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="E55:E56"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="L7:L8"/>
@@ -4343,16 +9434,14 @@
     <mergeCell ref="K27:K28"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="K25:K26"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="L27:L28"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="G25:G26"/>
     <mergeCell ref="E43:E44"/>
     <mergeCell ref="E45:E46"/>
     <mergeCell ref="E47:E48"/>
@@ -4367,6 +9456,29 @@
     <mergeCell ref="G43:G44"/>
     <mergeCell ref="H43:H44"/>
     <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="K43:K44"/>
+    <mergeCell ref="I43:J44"/>
+    <mergeCell ref="I45:J46"/>
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="I47:J48"/>
+    <mergeCell ref="I49:J50"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="K51:K52"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="O7:P8"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="R7:R8"/>
     <mergeCell ref="L53:L54"/>
     <mergeCell ref="L55:L56"/>
     <mergeCell ref="L41:L42"/>
@@ -4381,6 +9493,777 @@
     <mergeCell ref="L35:L36"/>
     <mergeCell ref="L37:L38"/>
     <mergeCell ref="L39:L40"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="O9:P10"/>
+    <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="R9:R10"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="O11:P12"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="O21:P22"/>
+    <mergeCell ref="Q21:Q22"/>
+    <mergeCell ref="R21:R22"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="O23:P24"/>
+    <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="R23:R24"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="O17:P18"/>
+    <mergeCell ref="Q17:Q18"/>
+    <mergeCell ref="R17:R18"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="O19:P20"/>
+    <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="R19:R20"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="O29:P30"/>
+    <mergeCell ref="Q29:Q30"/>
+    <mergeCell ref="R29:R30"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="N31:N32"/>
+    <mergeCell ref="O31:P32"/>
+    <mergeCell ref="Q31:Q32"/>
+    <mergeCell ref="R31:R32"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="O25:P26"/>
+    <mergeCell ref="Q25:Q26"/>
+    <mergeCell ref="R25:R26"/>
+    <mergeCell ref="M27:M28"/>
+    <mergeCell ref="N27:N28"/>
+    <mergeCell ref="O27:P28"/>
+    <mergeCell ref="Q27:Q28"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="M37:M38"/>
+    <mergeCell ref="N37:N38"/>
+    <mergeCell ref="O37:P38"/>
+    <mergeCell ref="Q37:Q38"/>
+    <mergeCell ref="R37:R38"/>
+    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="N39:N40"/>
+    <mergeCell ref="O39:P40"/>
+    <mergeCell ref="Q39:Q40"/>
+    <mergeCell ref="R39:R40"/>
+    <mergeCell ref="M33:M34"/>
+    <mergeCell ref="N33:N34"/>
+    <mergeCell ref="O33:P34"/>
+    <mergeCell ref="Q33:Q34"/>
+    <mergeCell ref="R33:R34"/>
+    <mergeCell ref="M35:M36"/>
+    <mergeCell ref="N35:N36"/>
+    <mergeCell ref="O35:P36"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="R35:R36"/>
+    <mergeCell ref="M45:M46"/>
+    <mergeCell ref="N45:N46"/>
+    <mergeCell ref="O45:P46"/>
+    <mergeCell ref="Q45:Q46"/>
+    <mergeCell ref="R45:R46"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="Q47:Q48"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="M41:M42"/>
+    <mergeCell ref="N41:N42"/>
+    <mergeCell ref="O41:P42"/>
+    <mergeCell ref="Q41:Q42"/>
+    <mergeCell ref="R41:R42"/>
+    <mergeCell ref="M43:M44"/>
+    <mergeCell ref="N43:N44"/>
+    <mergeCell ref="O43:P44"/>
+    <mergeCell ref="Q43:Q44"/>
+    <mergeCell ref="R43:R44"/>
+    <mergeCell ref="M53:M54"/>
+    <mergeCell ref="N53:N54"/>
+    <mergeCell ref="O53:P54"/>
+    <mergeCell ref="Q53:Q54"/>
+    <mergeCell ref="R53:R54"/>
+    <mergeCell ref="M55:M56"/>
+    <mergeCell ref="N55:N56"/>
+    <mergeCell ref="O55:P56"/>
+    <mergeCell ref="Q55:Q56"/>
+    <mergeCell ref="R55:R56"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="N49:N50"/>
+    <mergeCell ref="O49:P50"/>
+    <mergeCell ref="Q49:Q50"/>
+    <mergeCell ref="R49:R50"/>
+    <mergeCell ref="M51:M52"/>
+    <mergeCell ref="N51:N52"/>
+    <mergeCell ref="O51:P52"/>
+    <mergeCell ref="Q51:Q52"/>
+    <mergeCell ref="R51:R52"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:V10"/>
+    <mergeCell ref="W9:W10"/>
+    <mergeCell ref="X9:X10"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="U11:V12"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="U7:V8"/>
+    <mergeCell ref="W7:W8"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="S17:S18"/>
+    <mergeCell ref="T17:T18"/>
+    <mergeCell ref="U17:V18"/>
+    <mergeCell ref="W17:W18"/>
+    <mergeCell ref="X17:X18"/>
+    <mergeCell ref="S19:S20"/>
+    <mergeCell ref="T19:T20"/>
+    <mergeCell ref="U19:V20"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="X19:X20"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="U13:V14"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="T15:T16"/>
+    <mergeCell ref="U15:V16"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="X15:X16"/>
+    <mergeCell ref="S25:S26"/>
+    <mergeCell ref="T25:T26"/>
+    <mergeCell ref="U25:V26"/>
+    <mergeCell ref="W25:W26"/>
+    <mergeCell ref="X25:X26"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="T27:T28"/>
+    <mergeCell ref="U27:V28"/>
+    <mergeCell ref="W27:W28"/>
+    <mergeCell ref="X27:X28"/>
+    <mergeCell ref="S21:S22"/>
+    <mergeCell ref="T21:T22"/>
+    <mergeCell ref="U21:V22"/>
+    <mergeCell ref="W21:W22"/>
+    <mergeCell ref="X21:X22"/>
+    <mergeCell ref="S23:S24"/>
+    <mergeCell ref="T23:T24"/>
+    <mergeCell ref="U23:V24"/>
+    <mergeCell ref="W23:W24"/>
+    <mergeCell ref="X23:X24"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="T39:T40"/>
+    <mergeCell ref="U39:V40"/>
+    <mergeCell ref="W39:W40"/>
+    <mergeCell ref="X39:X40"/>
+    <mergeCell ref="S33:S34"/>
+    <mergeCell ref="T33:T34"/>
+    <mergeCell ref="U33:V34"/>
+    <mergeCell ref="W33:W34"/>
+    <mergeCell ref="X33:X34"/>
+    <mergeCell ref="S35:S36"/>
+    <mergeCell ref="T35:T36"/>
+    <mergeCell ref="U35:V36"/>
+    <mergeCell ref="W35:W36"/>
+    <mergeCell ref="X35:X36"/>
+    <mergeCell ref="S29:S30"/>
+    <mergeCell ref="T29:T30"/>
+    <mergeCell ref="U29:V30"/>
+    <mergeCell ref="W29:W30"/>
+    <mergeCell ref="X29:X30"/>
+    <mergeCell ref="S31:S32"/>
+    <mergeCell ref="T31:T32"/>
+    <mergeCell ref="U31:V32"/>
+    <mergeCell ref="W31:W32"/>
+    <mergeCell ref="X31:X32"/>
+    <mergeCell ref="S55:S56"/>
+    <mergeCell ref="T55:T56"/>
+    <mergeCell ref="U55:V56"/>
+    <mergeCell ref="W55:W56"/>
+    <mergeCell ref="X55:X56"/>
+    <mergeCell ref="S49:S50"/>
+    <mergeCell ref="T49:T50"/>
+    <mergeCell ref="U49:V50"/>
+    <mergeCell ref="W49:W50"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="S51:S52"/>
+    <mergeCell ref="T51:T52"/>
+    <mergeCell ref="U51:V52"/>
+    <mergeCell ref="W51:W52"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="S45:S46"/>
+    <mergeCell ref="T45:T46"/>
+    <mergeCell ref="U45:V46"/>
+    <mergeCell ref="W45:W46"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="S47:S48"/>
+    <mergeCell ref="T47:T48"/>
+    <mergeCell ref="U47:V48"/>
+    <mergeCell ref="W47:W48"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="Y2:AB2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="AI2:AJ2"/>
+    <mergeCell ref="AK2:AN2"/>
+    <mergeCell ref="AO2:AP2"/>
+    <mergeCell ref="AQ2:AT2"/>
+    <mergeCell ref="AU2:AV2"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="S53:S54"/>
+    <mergeCell ref="T53:T54"/>
+    <mergeCell ref="U53:V54"/>
+    <mergeCell ref="W53:W54"/>
+    <mergeCell ref="X53:X54"/>
+    <mergeCell ref="S41:S42"/>
+    <mergeCell ref="T41:T42"/>
+    <mergeCell ref="U41:V42"/>
+    <mergeCell ref="W41:W42"/>
+    <mergeCell ref="X41:X42"/>
+    <mergeCell ref="S43:S44"/>
+    <mergeCell ref="T43:T44"/>
+    <mergeCell ref="U43:V44"/>
+    <mergeCell ref="W43:W44"/>
+    <mergeCell ref="X43:X44"/>
+    <mergeCell ref="S37:S38"/>
+    <mergeCell ref="T37:T38"/>
+    <mergeCell ref="U37:V38"/>
+    <mergeCell ref="W37:W38"/>
+    <mergeCell ref="X37:X38"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="AG6:AH6"/>
+    <mergeCell ref="AM6:AN6"/>
+    <mergeCell ref="AS6:AT6"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:Z8"/>
+    <mergeCell ref="AA7:AB8"/>
+    <mergeCell ref="AC7:AC8"/>
+    <mergeCell ref="AD7:AD8"/>
+    <mergeCell ref="AE7:AE8"/>
+    <mergeCell ref="AF7:AF8"/>
+    <mergeCell ref="AG7:AH8"/>
+    <mergeCell ref="AI7:AI8"/>
+    <mergeCell ref="AJ7:AJ8"/>
+    <mergeCell ref="AK7:AK8"/>
+    <mergeCell ref="AL7:AL8"/>
+    <mergeCell ref="AM7:AN8"/>
+    <mergeCell ref="AO7:AO8"/>
+    <mergeCell ref="AP7:AP8"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="AR7:AR8"/>
+    <mergeCell ref="AS7:AT8"/>
+    <mergeCell ref="AV7:AV8"/>
+    <mergeCell ref="Y9:Y10"/>
+    <mergeCell ref="Z9:Z10"/>
+    <mergeCell ref="AA9:AB10"/>
+    <mergeCell ref="AC9:AC10"/>
+    <mergeCell ref="AD9:AD10"/>
+    <mergeCell ref="AE9:AE10"/>
+    <mergeCell ref="AF9:AF10"/>
+    <mergeCell ref="AG9:AH10"/>
+    <mergeCell ref="AI9:AI10"/>
+    <mergeCell ref="AJ9:AJ10"/>
+    <mergeCell ref="AK9:AK10"/>
+    <mergeCell ref="AL9:AL10"/>
+    <mergeCell ref="AM9:AN10"/>
+    <mergeCell ref="AO9:AO10"/>
+    <mergeCell ref="AP9:AP10"/>
+    <mergeCell ref="AQ9:AQ10"/>
+    <mergeCell ref="AR9:AR10"/>
+    <mergeCell ref="AS9:AT10"/>
+    <mergeCell ref="AU9:AU10"/>
+    <mergeCell ref="AV9:AV10"/>
+    <mergeCell ref="AL11:AL12"/>
+    <mergeCell ref="AM11:AN12"/>
+    <mergeCell ref="AO11:AO12"/>
+    <mergeCell ref="AP11:AP12"/>
+    <mergeCell ref="AQ11:AQ12"/>
+    <mergeCell ref="AR11:AR12"/>
+    <mergeCell ref="AS11:AT12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="AA11:AB12"/>
+    <mergeCell ref="AC11:AC12"/>
+    <mergeCell ref="AD11:AD12"/>
+    <mergeCell ref="AE11:AE12"/>
+    <mergeCell ref="AF11:AF12"/>
+    <mergeCell ref="AG11:AH12"/>
+    <mergeCell ref="AI11:AI12"/>
+    <mergeCell ref="AU7:AU8"/>
+    <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="AA15:AB16"/>
+    <mergeCell ref="AC15:AC16"/>
+    <mergeCell ref="AD15:AD16"/>
+    <mergeCell ref="AE15:AE16"/>
+    <mergeCell ref="AF15:AF16"/>
+    <mergeCell ref="AG15:AH16"/>
+    <mergeCell ref="AI15:AI16"/>
+    <mergeCell ref="AU11:AU12"/>
+    <mergeCell ref="AV11:AV12"/>
+    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="AA13:AB14"/>
+    <mergeCell ref="AC13:AC14"/>
+    <mergeCell ref="AD13:AD14"/>
+    <mergeCell ref="AE13:AE14"/>
+    <mergeCell ref="AF13:AF14"/>
+    <mergeCell ref="AG13:AH14"/>
+    <mergeCell ref="AI13:AI14"/>
+    <mergeCell ref="AJ13:AJ14"/>
+    <mergeCell ref="AK13:AK14"/>
+    <mergeCell ref="AL13:AL14"/>
+    <mergeCell ref="AM13:AN14"/>
+    <mergeCell ref="AO13:AO14"/>
+    <mergeCell ref="AP13:AP14"/>
+    <mergeCell ref="AQ13:AQ14"/>
+    <mergeCell ref="AR13:AR14"/>
+    <mergeCell ref="AS13:AT14"/>
+    <mergeCell ref="AU13:AU14"/>
+    <mergeCell ref="AV13:AV14"/>
+    <mergeCell ref="AJ11:AJ12"/>
+    <mergeCell ref="AK11:AK12"/>
+    <mergeCell ref="AU15:AU16"/>
+    <mergeCell ref="AV15:AV16"/>
+    <mergeCell ref="Y17:Y18"/>
+    <mergeCell ref="Z17:Z18"/>
+    <mergeCell ref="AA17:AB18"/>
+    <mergeCell ref="AC17:AC18"/>
+    <mergeCell ref="AD17:AD18"/>
+    <mergeCell ref="AE17:AE18"/>
+    <mergeCell ref="AF17:AF18"/>
+    <mergeCell ref="AG17:AH18"/>
+    <mergeCell ref="AI17:AI18"/>
+    <mergeCell ref="AJ17:AJ18"/>
+    <mergeCell ref="AK17:AK18"/>
+    <mergeCell ref="AL17:AL18"/>
+    <mergeCell ref="AM17:AN18"/>
+    <mergeCell ref="AO17:AO18"/>
+    <mergeCell ref="AP17:AP18"/>
+    <mergeCell ref="AQ17:AQ18"/>
+    <mergeCell ref="AR17:AR18"/>
+    <mergeCell ref="AS17:AT18"/>
+    <mergeCell ref="AU17:AU18"/>
+    <mergeCell ref="AV17:AV18"/>
+    <mergeCell ref="AJ15:AJ16"/>
+    <mergeCell ref="AK15:AK16"/>
+    <mergeCell ref="AL15:AL16"/>
+    <mergeCell ref="AM15:AN16"/>
+    <mergeCell ref="AO15:AO16"/>
+    <mergeCell ref="AP15:AP16"/>
+    <mergeCell ref="AQ15:AQ16"/>
+    <mergeCell ref="AR15:AR16"/>
+    <mergeCell ref="AS15:AT16"/>
+    <mergeCell ref="Y15:Y16"/>
+    <mergeCell ref="AV19:AV20"/>
+    <mergeCell ref="Y21:Y22"/>
+    <mergeCell ref="Z21:Z22"/>
+    <mergeCell ref="AA21:AB22"/>
+    <mergeCell ref="AC21:AC22"/>
+    <mergeCell ref="AD21:AD22"/>
+    <mergeCell ref="AE21:AE22"/>
+    <mergeCell ref="AF21:AF22"/>
+    <mergeCell ref="AG21:AH22"/>
+    <mergeCell ref="AI21:AI22"/>
+    <mergeCell ref="AJ21:AJ22"/>
+    <mergeCell ref="AK21:AK22"/>
+    <mergeCell ref="AL21:AL22"/>
+    <mergeCell ref="AM21:AN22"/>
+    <mergeCell ref="AO21:AO22"/>
+    <mergeCell ref="AP21:AP22"/>
+    <mergeCell ref="AQ21:AQ22"/>
+    <mergeCell ref="AR21:AR22"/>
+    <mergeCell ref="AS21:AT22"/>
+    <mergeCell ref="AU21:AU22"/>
+    <mergeCell ref="AV21:AV22"/>
+    <mergeCell ref="AJ19:AJ20"/>
+    <mergeCell ref="AK19:AK20"/>
+    <mergeCell ref="AL19:AL20"/>
+    <mergeCell ref="AM19:AN20"/>
+    <mergeCell ref="AO19:AO20"/>
+    <mergeCell ref="AP19:AP20"/>
+    <mergeCell ref="AQ19:AQ20"/>
+    <mergeCell ref="AR19:AR20"/>
+    <mergeCell ref="AS19:AT20"/>
+    <mergeCell ref="Y19:Y20"/>
+    <mergeCell ref="Z19:Z20"/>
+    <mergeCell ref="AL23:AL24"/>
+    <mergeCell ref="AM23:AN24"/>
+    <mergeCell ref="AO23:AO24"/>
+    <mergeCell ref="AP23:AP24"/>
+    <mergeCell ref="AQ23:AQ24"/>
+    <mergeCell ref="AR23:AR24"/>
+    <mergeCell ref="AS23:AT24"/>
+    <mergeCell ref="Y23:Y24"/>
+    <mergeCell ref="Z23:Z24"/>
+    <mergeCell ref="AA23:AB24"/>
+    <mergeCell ref="AC23:AC24"/>
+    <mergeCell ref="AD23:AD24"/>
+    <mergeCell ref="AE23:AE24"/>
+    <mergeCell ref="AF23:AF24"/>
+    <mergeCell ref="AG23:AH24"/>
+    <mergeCell ref="AI23:AI24"/>
+    <mergeCell ref="AU19:AU20"/>
+    <mergeCell ref="AA19:AB20"/>
+    <mergeCell ref="AC19:AC20"/>
+    <mergeCell ref="AD19:AD20"/>
+    <mergeCell ref="AE19:AE20"/>
+    <mergeCell ref="AF19:AF20"/>
+    <mergeCell ref="AG19:AH20"/>
+    <mergeCell ref="AI19:AI20"/>
+    <mergeCell ref="Z27:Z28"/>
+    <mergeCell ref="AA27:AB28"/>
+    <mergeCell ref="AC27:AC28"/>
+    <mergeCell ref="AD27:AD28"/>
+    <mergeCell ref="AE27:AE28"/>
+    <mergeCell ref="AF27:AF28"/>
+    <mergeCell ref="AG27:AH28"/>
+    <mergeCell ref="AI27:AI28"/>
+    <mergeCell ref="AU23:AU24"/>
+    <mergeCell ref="AV23:AV24"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="Z25:Z26"/>
+    <mergeCell ref="AA25:AB26"/>
+    <mergeCell ref="AC25:AC26"/>
+    <mergeCell ref="AD25:AD26"/>
+    <mergeCell ref="AE25:AE26"/>
+    <mergeCell ref="AF25:AF26"/>
+    <mergeCell ref="AG25:AH26"/>
+    <mergeCell ref="AI25:AI26"/>
+    <mergeCell ref="AJ25:AJ26"/>
+    <mergeCell ref="AK25:AK26"/>
+    <mergeCell ref="AL25:AL26"/>
+    <mergeCell ref="AM25:AN26"/>
+    <mergeCell ref="AO25:AO26"/>
+    <mergeCell ref="AP25:AP26"/>
+    <mergeCell ref="AQ25:AQ26"/>
+    <mergeCell ref="AR25:AR26"/>
+    <mergeCell ref="AS25:AT26"/>
+    <mergeCell ref="AU25:AU26"/>
+    <mergeCell ref="AV25:AV26"/>
+    <mergeCell ref="AJ23:AJ24"/>
+    <mergeCell ref="AK23:AK24"/>
+    <mergeCell ref="AU27:AU28"/>
+    <mergeCell ref="AV27:AV28"/>
+    <mergeCell ref="Y29:Y30"/>
+    <mergeCell ref="Z29:Z30"/>
+    <mergeCell ref="AA29:AB30"/>
+    <mergeCell ref="AC29:AC30"/>
+    <mergeCell ref="AD29:AD30"/>
+    <mergeCell ref="AE29:AE30"/>
+    <mergeCell ref="AF29:AF30"/>
+    <mergeCell ref="AG29:AH30"/>
+    <mergeCell ref="AI29:AI30"/>
+    <mergeCell ref="AJ29:AJ30"/>
+    <mergeCell ref="AK29:AK30"/>
+    <mergeCell ref="AL29:AL30"/>
+    <mergeCell ref="AM29:AN30"/>
+    <mergeCell ref="AO29:AO30"/>
+    <mergeCell ref="AP29:AP30"/>
+    <mergeCell ref="AQ29:AQ30"/>
+    <mergeCell ref="AR29:AR30"/>
+    <mergeCell ref="AS29:AT30"/>
+    <mergeCell ref="AU29:AU30"/>
+    <mergeCell ref="AV29:AV30"/>
+    <mergeCell ref="AJ27:AJ28"/>
+    <mergeCell ref="AK27:AK28"/>
+    <mergeCell ref="AL27:AL28"/>
+    <mergeCell ref="AM27:AN28"/>
+    <mergeCell ref="AO27:AO28"/>
+    <mergeCell ref="AP27:AP28"/>
+    <mergeCell ref="AQ27:AQ28"/>
+    <mergeCell ref="AR27:AR28"/>
+    <mergeCell ref="AS27:AT28"/>
+    <mergeCell ref="Y27:Y28"/>
+    <mergeCell ref="AV31:AV32"/>
+    <mergeCell ref="Y33:Y34"/>
+    <mergeCell ref="Z33:Z34"/>
+    <mergeCell ref="AA33:AB34"/>
+    <mergeCell ref="AC33:AC34"/>
+    <mergeCell ref="AD33:AD34"/>
+    <mergeCell ref="AE33:AE34"/>
+    <mergeCell ref="AF33:AF34"/>
+    <mergeCell ref="AG33:AH34"/>
+    <mergeCell ref="AI33:AI34"/>
+    <mergeCell ref="AJ33:AJ34"/>
+    <mergeCell ref="AK33:AK34"/>
+    <mergeCell ref="AL33:AL34"/>
+    <mergeCell ref="AM33:AN34"/>
+    <mergeCell ref="AO33:AO34"/>
+    <mergeCell ref="AP33:AP34"/>
+    <mergeCell ref="AQ33:AQ34"/>
+    <mergeCell ref="AR33:AR34"/>
+    <mergeCell ref="AS33:AT34"/>
+    <mergeCell ref="AU33:AU34"/>
+    <mergeCell ref="AV33:AV34"/>
+    <mergeCell ref="AJ31:AJ32"/>
+    <mergeCell ref="AK31:AK32"/>
+    <mergeCell ref="AL31:AL32"/>
+    <mergeCell ref="AM31:AN32"/>
+    <mergeCell ref="AO31:AO32"/>
+    <mergeCell ref="AP31:AP32"/>
+    <mergeCell ref="AQ31:AQ32"/>
+    <mergeCell ref="AR31:AR32"/>
+    <mergeCell ref="AS31:AT32"/>
+    <mergeCell ref="Y31:Y32"/>
+    <mergeCell ref="Z31:Z32"/>
+    <mergeCell ref="AL35:AL36"/>
+    <mergeCell ref="AM35:AN36"/>
+    <mergeCell ref="AO35:AO36"/>
+    <mergeCell ref="AP35:AP36"/>
+    <mergeCell ref="AQ35:AQ36"/>
+    <mergeCell ref="AR35:AR36"/>
+    <mergeCell ref="AS35:AT36"/>
+    <mergeCell ref="Y35:Y36"/>
+    <mergeCell ref="Z35:Z36"/>
+    <mergeCell ref="AA35:AB36"/>
+    <mergeCell ref="AC35:AC36"/>
+    <mergeCell ref="AD35:AD36"/>
+    <mergeCell ref="AE35:AE36"/>
+    <mergeCell ref="AF35:AF36"/>
+    <mergeCell ref="AG35:AH36"/>
+    <mergeCell ref="AI35:AI36"/>
+    <mergeCell ref="AU31:AU32"/>
+    <mergeCell ref="AA31:AB32"/>
+    <mergeCell ref="AC31:AC32"/>
+    <mergeCell ref="AD31:AD32"/>
+    <mergeCell ref="AE31:AE32"/>
+    <mergeCell ref="AF31:AF32"/>
+    <mergeCell ref="AG31:AH32"/>
+    <mergeCell ref="AI31:AI32"/>
+    <mergeCell ref="Z39:Z40"/>
+    <mergeCell ref="AA39:AB40"/>
+    <mergeCell ref="AC39:AC40"/>
+    <mergeCell ref="AD39:AD40"/>
+    <mergeCell ref="AE39:AE40"/>
+    <mergeCell ref="AF39:AF40"/>
+    <mergeCell ref="AG39:AH40"/>
+    <mergeCell ref="AI39:AI40"/>
+    <mergeCell ref="AU35:AU36"/>
+    <mergeCell ref="AV35:AV36"/>
+    <mergeCell ref="Y37:Y38"/>
+    <mergeCell ref="Z37:Z38"/>
+    <mergeCell ref="AA37:AB38"/>
+    <mergeCell ref="AC37:AC38"/>
+    <mergeCell ref="AD37:AD38"/>
+    <mergeCell ref="AE37:AE38"/>
+    <mergeCell ref="AF37:AF38"/>
+    <mergeCell ref="AG37:AH38"/>
+    <mergeCell ref="AI37:AI38"/>
+    <mergeCell ref="AJ37:AJ38"/>
+    <mergeCell ref="AK37:AK38"/>
+    <mergeCell ref="AL37:AL38"/>
+    <mergeCell ref="AM37:AN38"/>
+    <mergeCell ref="AO37:AO38"/>
+    <mergeCell ref="AP37:AP38"/>
+    <mergeCell ref="AQ37:AQ38"/>
+    <mergeCell ref="AR37:AR38"/>
+    <mergeCell ref="AS37:AT38"/>
+    <mergeCell ref="AU37:AU38"/>
+    <mergeCell ref="AV37:AV38"/>
+    <mergeCell ref="AJ35:AJ36"/>
+    <mergeCell ref="AK35:AK36"/>
+    <mergeCell ref="AU39:AU40"/>
+    <mergeCell ref="AV39:AV40"/>
+    <mergeCell ref="Y41:Y42"/>
+    <mergeCell ref="Z41:Z42"/>
+    <mergeCell ref="AA41:AB42"/>
+    <mergeCell ref="AC41:AC42"/>
+    <mergeCell ref="AD41:AD42"/>
+    <mergeCell ref="AE41:AE42"/>
+    <mergeCell ref="AF41:AF42"/>
+    <mergeCell ref="AG41:AH42"/>
+    <mergeCell ref="AI41:AI42"/>
+    <mergeCell ref="AJ41:AJ42"/>
+    <mergeCell ref="AK41:AK42"/>
+    <mergeCell ref="AL41:AL42"/>
+    <mergeCell ref="AM41:AN42"/>
+    <mergeCell ref="AO41:AO42"/>
+    <mergeCell ref="AP41:AP42"/>
+    <mergeCell ref="AQ41:AQ42"/>
+    <mergeCell ref="AR41:AR42"/>
+    <mergeCell ref="AS41:AT42"/>
+    <mergeCell ref="AU41:AU42"/>
+    <mergeCell ref="AV41:AV42"/>
+    <mergeCell ref="AJ39:AJ40"/>
+    <mergeCell ref="AK39:AK40"/>
+    <mergeCell ref="AL39:AL40"/>
+    <mergeCell ref="AM39:AN40"/>
+    <mergeCell ref="AO39:AO40"/>
+    <mergeCell ref="AP39:AP40"/>
+    <mergeCell ref="AQ39:AQ40"/>
+    <mergeCell ref="AR39:AR40"/>
+    <mergeCell ref="AS39:AT40"/>
+    <mergeCell ref="Y39:Y40"/>
+    <mergeCell ref="AV43:AV44"/>
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="AA45:AB46"/>
+    <mergeCell ref="AC45:AC46"/>
+    <mergeCell ref="AD45:AD46"/>
+    <mergeCell ref="AE45:AE46"/>
+    <mergeCell ref="AF45:AF46"/>
+    <mergeCell ref="AG45:AH46"/>
+    <mergeCell ref="AI45:AI46"/>
+    <mergeCell ref="AJ45:AJ46"/>
+    <mergeCell ref="AK45:AK46"/>
+    <mergeCell ref="AL45:AL46"/>
+    <mergeCell ref="AM45:AN46"/>
+    <mergeCell ref="AO45:AO46"/>
+    <mergeCell ref="AP45:AP46"/>
+    <mergeCell ref="AQ45:AQ46"/>
+    <mergeCell ref="AR45:AR46"/>
+    <mergeCell ref="AS45:AT46"/>
+    <mergeCell ref="AU45:AU46"/>
+    <mergeCell ref="AV45:AV46"/>
+    <mergeCell ref="AJ43:AJ44"/>
+    <mergeCell ref="AK43:AK44"/>
+    <mergeCell ref="AL43:AL44"/>
+    <mergeCell ref="AM43:AN44"/>
+    <mergeCell ref="AO43:AO44"/>
+    <mergeCell ref="AP43:AP44"/>
+    <mergeCell ref="AQ43:AQ44"/>
+    <mergeCell ref="AR43:AR44"/>
+    <mergeCell ref="AS43:AT44"/>
+    <mergeCell ref="Y43:Y44"/>
+    <mergeCell ref="Z43:Z44"/>
+    <mergeCell ref="AL47:AL48"/>
+    <mergeCell ref="AM47:AN48"/>
+    <mergeCell ref="AO47:AO48"/>
+    <mergeCell ref="AP47:AP48"/>
+    <mergeCell ref="AQ47:AQ48"/>
+    <mergeCell ref="AR47:AR48"/>
+    <mergeCell ref="AS47:AT48"/>
+    <mergeCell ref="Y47:Y48"/>
+    <mergeCell ref="Z47:Z48"/>
+    <mergeCell ref="AA47:AB48"/>
+    <mergeCell ref="AC47:AC48"/>
+    <mergeCell ref="AD47:AD48"/>
+    <mergeCell ref="AE47:AE48"/>
+    <mergeCell ref="AF47:AF48"/>
+    <mergeCell ref="AG47:AH48"/>
+    <mergeCell ref="AI47:AI48"/>
+    <mergeCell ref="AU43:AU44"/>
+    <mergeCell ref="AA43:AB44"/>
+    <mergeCell ref="AC43:AC44"/>
+    <mergeCell ref="AD43:AD44"/>
+    <mergeCell ref="AE43:AE44"/>
+    <mergeCell ref="AF43:AF44"/>
+    <mergeCell ref="AG43:AH44"/>
+    <mergeCell ref="AI43:AI44"/>
+    <mergeCell ref="Z51:Z52"/>
+    <mergeCell ref="AA51:AB52"/>
+    <mergeCell ref="AC51:AC52"/>
+    <mergeCell ref="AD51:AD52"/>
+    <mergeCell ref="AE51:AE52"/>
+    <mergeCell ref="AF51:AF52"/>
+    <mergeCell ref="AG51:AH52"/>
+    <mergeCell ref="AI51:AI52"/>
+    <mergeCell ref="AU47:AU48"/>
+    <mergeCell ref="AV47:AV48"/>
+    <mergeCell ref="Y49:Y50"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="AA49:AB50"/>
+    <mergeCell ref="AC49:AC50"/>
+    <mergeCell ref="AD49:AD50"/>
+    <mergeCell ref="AE49:AE50"/>
+    <mergeCell ref="AF49:AF50"/>
+    <mergeCell ref="AG49:AH50"/>
+    <mergeCell ref="AI49:AI50"/>
+    <mergeCell ref="AJ49:AJ50"/>
+    <mergeCell ref="AK49:AK50"/>
+    <mergeCell ref="AL49:AL50"/>
+    <mergeCell ref="AM49:AN50"/>
+    <mergeCell ref="AO49:AO50"/>
+    <mergeCell ref="AP49:AP50"/>
+    <mergeCell ref="AQ49:AQ50"/>
+    <mergeCell ref="AR49:AR50"/>
+    <mergeCell ref="AS49:AT50"/>
+    <mergeCell ref="AU49:AU50"/>
+    <mergeCell ref="AV49:AV50"/>
+    <mergeCell ref="AJ47:AJ48"/>
+    <mergeCell ref="AK47:AK48"/>
+    <mergeCell ref="AU51:AU52"/>
+    <mergeCell ref="AV51:AV52"/>
+    <mergeCell ref="Y53:Y54"/>
+    <mergeCell ref="Z53:Z54"/>
+    <mergeCell ref="AA53:AB54"/>
+    <mergeCell ref="AC53:AC54"/>
+    <mergeCell ref="AD53:AD54"/>
+    <mergeCell ref="AE53:AE54"/>
+    <mergeCell ref="AF53:AF54"/>
+    <mergeCell ref="AG53:AH54"/>
+    <mergeCell ref="AI53:AI54"/>
+    <mergeCell ref="AJ53:AJ54"/>
+    <mergeCell ref="AK53:AK54"/>
+    <mergeCell ref="AL53:AL54"/>
+    <mergeCell ref="AM53:AN54"/>
+    <mergeCell ref="AO53:AO54"/>
+    <mergeCell ref="AP53:AP54"/>
+    <mergeCell ref="AQ53:AQ54"/>
+    <mergeCell ref="AR53:AR54"/>
+    <mergeCell ref="AS53:AT54"/>
+    <mergeCell ref="AU53:AU54"/>
+    <mergeCell ref="AV53:AV54"/>
+    <mergeCell ref="AJ51:AJ52"/>
+    <mergeCell ref="AK51:AK52"/>
+    <mergeCell ref="AL51:AL52"/>
+    <mergeCell ref="AM51:AN52"/>
+    <mergeCell ref="AO51:AO52"/>
+    <mergeCell ref="AP51:AP52"/>
+    <mergeCell ref="AQ51:AQ52"/>
+    <mergeCell ref="AR51:AR52"/>
+    <mergeCell ref="AS51:AT52"/>
+    <mergeCell ref="Y51:Y52"/>
+    <mergeCell ref="AU55:AU56"/>
+    <mergeCell ref="AV55:AV56"/>
+    <mergeCell ref="AJ55:AJ56"/>
+    <mergeCell ref="AK55:AK56"/>
+    <mergeCell ref="AL55:AL56"/>
+    <mergeCell ref="AM55:AN56"/>
+    <mergeCell ref="AO55:AO56"/>
+    <mergeCell ref="AP55:AP56"/>
+    <mergeCell ref="AQ55:AQ56"/>
+    <mergeCell ref="AR55:AR56"/>
+    <mergeCell ref="AS55:AT56"/>
+    <mergeCell ref="Y55:Y56"/>
+    <mergeCell ref="Z55:Z56"/>
+    <mergeCell ref="AA55:AB56"/>
+    <mergeCell ref="AC55:AC56"/>
+    <mergeCell ref="AD55:AD56"/>
+    <mergeCell ref="AE55:AE56"/>
+    <mergeCell ref="AF55:AF56"/>
+    <mergeCell ref="AG55:AH56"/>
+    <mergeCell ref="AI55:AI56"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.23622047244094491" right="0.15748031496062992" top="0.51181102362204722" bottom="0.15748031496062992" header="0.15748031496062992" footer="0.15748031496062992"/>
@@ -4421,19 +10304,19 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
       <c r="D2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="E2" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
       <c r="H2" s="13" t="s">
         <v>6</v>
       </c>
@@ -4453,18 +10336,18 @@
         <v>1</v>
       </c>
       <c r="B4" s="14"/>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="61"/>
+      <c r="D4" s="68"/>
       <c r="E4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="14"/>
-      <c r="G4" s="60" t="s">
+      <c r="G4" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="61"/>
+      <c r="H4" s="68"/>
     </row>
     <row r="5" spans="1:8" ht="14.25" thickBot="1" x14ac:dyDescent="0.15">
       <c r="A5" s="6"/>
@@ -4499,16 +10382,16 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A7" s="34"/>
-      <c r="B7" s="51"/>
+      <c r="A7" s="60"/>
+      <c r="B7" s="50"/>
       <c r="C7" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="51"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="50"/>
       <c r="G7" s="15" t="s">
         <v>14</v>
       </c>
@@ -4517,30 +10400,30 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A8" s="35"/>
-      <c r="B8" s="52"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="51"/>
       <c r="C8" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="63"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="52"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="51"/>
       <c r="G8" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="63"/>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A9" s="34"/>
-      <c r="B9" s="48"/>
+      <c r="A9" s="60"/>
+      <c r="B9" s="31"/>
       <c r="C9" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="34"/>
-      <c r="F9" s="48"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="31"/>
       <c r="G9" s="15" t="s">
         <v>14</v>
       </c>
@@ -4549,30 +10432,30 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A10" s="35"/>
-      <c r="B10" s="49"/>
+      <c r="A10" s="61"/>
+      <c r="B10" s="40"/>
       <c r="C10" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="63"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="49"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="63"/>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A11" s="34"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="60"/>
+      <c r="B11" s="31"/>
       <c r="C11" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="48"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="31"/>
       <c r="G11" s="15" t="s">
         <v>14</v>
       </c>
@@ -4581,30 +10464,30 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A12" s="35"/>
-      <c r="B12" s="49"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="40"/>
       <c r="C12" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="63"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="49"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="40"/>
       <c r="G12" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="63"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A13" s="34"/>
-      <c r="B13" s="48"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="31"/>
       <c r="C13" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="48"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="31"/>
       <c r="G13" s="15" t="s">
         <v>14</v>
       </c>
@@ -4613,30 +10496,30 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A14" s="35"/>
-      <c r="B14" s="49"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="40"/>
       <c r="C14" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="63"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="49"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="40"/>
       <c r="G14" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="63"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A15" s="34"/>
-      <c r="B15" s="48"/>
+      <c r="A15" s="60"/>
+      <c r="B15" s="31"/>
       <c r="C15" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="34"/>
-      <c r="F15" s="48"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="31"/>
       <c r="G15" s="15" t="s">
         <v>14</v>
       </c>
@@ -4645,30 +10528,30 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A16" s="35"/>
-      <c r="B16" s="49"/>
+      <c r="A16" s="61"/>
+      <c r="B16" s="40"/>
       <c r="C16" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="63"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="49"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="40"/>
       <c r="G16" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="63"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A17" s="34"/>
-      <c r="B17" s="36"/>
+      <c r="A17" s="60"/>
+      <c r="B17" s="31"/>
       <c r="C17" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="36"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="31"/>
       <c r="G17" s="15" t="s">
         <v>14</v>
       </c>
@@ -4677,30 +10560,30 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A18" s="35"/>
-      <c r="B18" s="38"/>
+      <c r="A18" s="61"/>
+      <c r="B18" s="40"/>
       <c r="C18" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="63"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="38"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="40"/>
       <c r="G18" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="63"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A19" s="34"/>
-      <c r="B19" s="36"/>
+      <c r="A19" s="60"/>
+      <c r="B19" s="31"/>
       <c r="C19" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="36"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="31"/>
       <c r="G19" s="15" t="s">
         <v>14</v>
       </c>
@@ -4709,30 +10592,30 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A20" s="35"/>
-      <c r="B20" s="38"/>
+      <c r="A20" s="61"/>
+      <c r="B20" s="40"/>
       <c r="C20" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="63"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="38"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="40"/>
       <c r="G20" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="63"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A21" s="34"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="60"/>
+      <c r="B21" s="31"/>
       <c r="C21" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="34"/>
-      <c r="F21" s="36"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="31"/>
       <c r="G21" s="15" t="s">
         <v>14</v>
       </c>
@@ -4741,30 +10624,30 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A22" s="35"/>
-      <c r="B22" s="38"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="40"/>
       <c r="C22" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="63"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="38"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="40"/>
       <c r="G22" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H22" s="63"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A23" s="34"/>
-      <c r="B23" s="47"/>
+      <c r="A23" s="60"/>
+      <c r="B23" s="46"/>
       <c r="C23" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D23" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="34"/>
-      <c r="F23" s="47"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="46"/>
       <c r="G23" s="15" t="s">
         <v>14</v>
       </c>
@@ -4773,30 +10656,30 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A24" s="35"/>
-      <c r="B24" s="38"/>
+      <c r="A24" s="61"/>
+      <c r="B24" s="40"/>
       <c r="C24" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D24" s="63"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="38"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="40"/>
       <c r="G24" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="63"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A25" s="34"/>
-      <c r="B25" s="48"/>
+      <c r="A25" s="60"/>
+      <c r="B25" s="31"/>
       <c r="C25" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="34"/>
-      <c r="F25" s="48"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="31"/>
       <c r="G25" s="15" t="s">
         <v>14</v>
       </c>
@@ -4805,30 +10688,30 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A26" s="35"/>
-      <c r="B26" s="49"/>
+      <c r="A26" s="61"/>
+      <c r="B26" s="40"/>
       <c r="C26" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D26" s="63"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="49"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="40"/>
       <c r="G26" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="63"/>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A27" s="34"/>
-      <c r="B27" s="36"/>
+      <c r="A27" s="60"/>
+      <c r="B27" s="31"/>
       <c r="C27" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="34"/>
-      <c r="F27" s="36"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="31"/>
       <c r="G27" s="15" t="s">
         <v>14</v>
       </c>
@@ -4837,30 +10720,30 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A28" s="35"/>
-      <c r="B28" s="38"/>
+      <c r="A28" s="61"/>
+      <c r="B28" s="40"/>
       <c r="C28" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="63"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="38"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="40"/>
       <c r="G28" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H28" s="63"/>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A29" s="34"/>
-      <c r="B29" s="36"/>
+      <c r="A29" s="60"/>
+      <c r="B29" s="31"/>
       <c r="C29" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D29" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="34"/>
-      <c r="F29" s="36"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="31"/>
       <c r="G29" s="15" t="s">
         <v>14</v>
       </c>
@@ -4869,30 +10752,30 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A30" s="35"/>
-      <c r="B30" s="38"/>
+      <c r="A30" s="61"/>
+      <c r="B30" s="40"/>
       <c r="C30" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="63"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="38"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="40"/>
       <c r="G30" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H30" s="63"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A31" s="34"/>
-      <c r="B31" s="36"/>
+      <c r="A31" s="60"/>
+      <c r="B31" s="31"/>
       <c r="C31" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E31" s="34"/>
-      <c r="F31" s="36"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="31"/>
       <c r="G31" s="15" t="s">
         <v>14</v>
       </c>
@@ -4901,30 +10784,30 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A32" s="35"/>
-      <c r="B32" s="38"/>
+      <c r="A32" s="61"/>
+      <c r="B32" s="40"/>
       <c r="C32" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D32" s="63"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="38"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="40"/>
       <c r="G32" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H32" s="63"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A33" s="34"/>
-      <c r="B33" s="47"/>
+      <c r="A33" s="60"/>
+      <c r="B33" s="46"/>
       <c r="C33" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D33" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="34"/>
-      <c r="F33" s="47"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="46"/>
       <c r="G33" s="15" t="s">
         <v>14</v>
       </c>
@@ -4933,30 +10816,30 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A34" s="35"/>
-      <c r="B34" s="38"/>
+      <c r="A34" s="61"/>
+      <c r="B34" s="40"/>
       <c r="C34" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="63"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="38"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="40"/>
       <c r="G34" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H34" s="63"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A35" s="34"/>
-      <c r="B35" s="48"/>
+      <c r="A35" s="60"/>
+      <c r="B35" s="31"/>
       <c r="C35" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="34"/>
-      <c r="F35" s="48"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="31"/>
       <c r="G35" s="15" t="s">
         <v>14</v>
       </c>
@@ -4965,30 +10848,30 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A36" s="35"/>
-      <c r="B36" s="49"/>
+      <c r="A36" s="61"/>
+      <c r="B36" s="40"/>
       <c r="C36" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D36" s="63"/>
-      <c r="E36" s="35"/>
-      <c r="F36" s="49"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="40"/>
       <c r="G36" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H36" s="63"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A37" s="34"/>
-      <c r="B37" s="48"/>
+      <c r="A37" s="60"/>
+      <c r="B37" s="31"/>
       <c r="C37" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="34"/>
-      <c r="F37" s="48"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="31"/>
       <c r="G37" s="15" t="s">
         <v>14</v>
       </c>
@@ -4997,30 +10880,30 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A38" s="35"/>
-      <c r="B38" s="49"/>
+      <c r="A38" s="61"/>
+      <c r="B38" s="40"/>
       <c r="C38" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="63"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="49"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="40"/>
       <c r="G38" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H38" s="63"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A39" s="34"/>
-      <c r="B39" s="48"/>
+      <c r="A39" s="60"/>
+      <c r="B39" s="31"/>
       <c r="C39" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D39" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="34"/>
-      <c r="F39" s="48"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="31"/>
       <c r="G39" s="15" t="s">
         <v>14</v>
       </c>
@@ -5029,30 +10912,30 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A40" s="35"/>
-      <c r="B40" s="49"/>
+      <c r="A40" s="61"/>
+      <c r="B40" s="40"/>
       <c r="C40" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D40" s="63"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="49"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="40"/>
       <c r="G40" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H40" s="63"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A41" s="34"/>
-      <c r="B41" s="48"/>
+      <c r="A41" s="60"/>
+      <c r="B41" s="31"/>
       <c r="C41" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D41" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="34"/>
-      <c r="F41" s="48"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="31"/>
       <c r="G41" s="15" t="s">
         <v>14</v>
       </c>
@@ -5061,30 +10944,30 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A42" s="35"/>
-      <c r="B42" s="49"/>
+      <c r="A42" s="61"/>
+      <c r="B42" s="40"/>
       <c r="C42" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="63"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="49"/>
+      <c r="E42" s="61"/>
+      <c r="F42" s="40"/>
       <c r="G42" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H42" s="63"/>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A43" s="34"/>
-      <c r="B43" s="48"/>
+      <c r="A43" s="60"/>
+      <c r="B43" s="31"/>
       <c r="C43" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D43" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="34"/>
-      <c r="F43" s="48"/>
+      <c r="E43" s="60"/>
+      <c r="F43" s="31"/>
       <c r="G43" s="15" t="s">
         <v>14</v>
       </c>
@@ -5093,30 +10976,30 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A44" s="35"/>
-      <c r="B44" s="49"/>
+      <c r="A44" s="61"/>
+      <c r="B44" s="40"/>
       <c r="C44" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D44" s="63"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="49"/>
+      <c r="E44" s="61"/>
+      <c r="F44" s="40"/>
       <c r="G44" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H44" s="63"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A45" s="34"/>
-      <c r="B45" s="48"/>
+      <c r="A45" s="60"/>
+      <c r="B45" s="31"/>
       <c r="C45" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D45" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="34"/>
-      <c r="F45" s="48"/>
+      <c r="E45" s="60"/>
+      <c r="F45" s="31"/>
       <c r="G45" s="15" t="s">
         <v>14</v>
       </c>
@@ -5125,30 +11008,30 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A46" s="35"/>
-      <c r="B46" s="49"/>
+      <c r="A46" s="61"/>
+      <c r="B46" s="40"/>
       <c r="C46" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D46" s="63"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="49"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="40"/>
       <c r="G46" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H46" s="63"/>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A47" s="34"/>
-      <c r="B47" s="36"/>
+      <c r="A47" s="60"/>
+      <c r="B47" s="31"/>
       <c r="C47" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D47" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="34"/>
-      <c r="F47" s="36"/>
+      <c r="E47" s="60"/>
+      <c r="F47" s="31"/>
       <c r="G47" s="15" t="s">
         <v>14</v>
       </c>
@@ -5157,30 +11040,30 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A48" s="35"/>
-      <c r="B48" s="38"/>
+      <c r="A48" s="61"/>
+      <c r="B48" s="40"/>
       <c r="C48" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D48" s="63"/>
-      <c r="E48" s="35"/>
-      <c r="F48" s="38"/>
+      <c r="E48" s="61"/>
+      <c r="F48" s="40"/>
       <c r="G48" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H48" s="63"/>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A49" s="34"/>
-      <c r="B49" s="36"/>
+      <c r="A49" s="60"/>
+      <c r="B49" s="31"/>
       <c r="C49" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D49" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E49" s="34"/>
-      <c r="F49" s="36"/>
+      <c r="E49" s="60"/>
+      <c r="F49" s="31"/>
       <c r="G49" s="15" t="s">
         <v>14</v>
       </c>
@@ -5189,30 +11072,30 @@
       </c>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A50" s="35"/>
-      <c r="B50" s="38"/>
+      <c r="A50" s="61"/>
+      <c r="B50" s="40"/>
       <c r="C50" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D50" s="63"/>
-      <c r="E50" s="35"/>
-      <c r="F50" s="38"/>
+      <c r="E50" s="61"/>
+      <c r="F50" s="40"/>
       <c r="G50" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H50" s="63"/>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A51" s="34"/>
-      <c r="B51" s="36"/>
+      <c r="A51" s="60"/>
+      <c r="B51" s="31"/>
       <c r="C51" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="34"/>
-      <c r="F51" s="36"/>
+      <c r="E51" s="60"/>
+      <c r="F51" s="31"/>
       <c r="G51" s="15" t="s">
         <v>14</v>
       </c>
@@ -5221,30 +11104,30 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A52" s="35"/>
-      <c r="B52" s="38"/>
+      <c r="A52" s="61"/>
+      <c r="B52" s="40"/>
       <c r="C52" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D52" s="63"/>
-      <c r="E52" s="35"/>
-      <c r="F52" s="38"/>
+      <c r="E52" s="61"/>
+      <c r="F52" s="40"/>
       <c r="G52" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H52" s="63"/>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A53" s="34"/>
-      <c r="B53" s="36"/>
+      <c r="A53" s="60"/>
+      <c r="B53" s="31"/>
       <c r="C53" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D53" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E53" s="34"/>
-      <c r="F53" s="36"/>
+      <c r="E53" s="60"/>
+      <c r="F53" s="31"/>
       <c r="G53" s="15" t="s">
         <v>14</v>
       </c>
@@ -5253,46 +11136,46 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A54" s="35"/>
-      <c r="B54" s="38"/>
+      <c r="A54" s="61"/>
+      <c r="B54" s="40"/>
       <c r="C54" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D54" s="63"/>
-      <c r="E54" s="35"/>
-      <c r="F54" s="38"/>
+      <c r="E54" s="61"/>
+      <c r="F54" s="40"/>
       <c r="G54" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H54" s="63"/>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.1">
-      <c r="A55" s="34"/>
-      <c r="B55" s="36"/>
+      <c r="A55" s="60"/>
+      <c r="B55" s="31"/>
       <c r="C55" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D55" s="65" t="s">
+      <c r="D55" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E55" s="34"/>
-      <c r="F55" s="36"/>
+      <c r="E55" s="60"/>
+      <c r="F55" s="31"/>
       <c r="G55" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H55" s="65" t="s">
+      <c r="H55" s="62" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.15">
       <c r="A56" s="64"/>
-      <c r="B56" s="37"/>
+      <c r="B56" s="65"/>
       <c r="C56" s="17" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="66"/>
       <c r="E56" s="64"/>
-      <c r="F56" s="37"/>
+      <c r="F56" s="65"/>
       <c r="G56" s="17" t="s">
         <v>15</v>
       </c>
@@ -5377,7 +11260,6 @@
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="H11:H12"/>
-    <mergeCell ref="D13:D14"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="D7:D8"/>
@@ -5388,6 +11270,7 @@
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="D9:D10"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="D39:D40"/>
@@ -5397,6 +11280,15 @@
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="D23:D24"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="D25:D26"/>
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="B45:B46"/>
     <mergeCell ref="D45:D46"/>
@@ -5430,16 +11322,11 @@
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="D47:D48"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="D21:D22"/>
@@ -5449,11 +11336,7 @@
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="D17:D18"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.9055118110236221" right="0.70866141732283472" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
